--- a/outputs/stage_01/nsr10_spectra/data/case_01_nsr10_spectra.xlsx
+++ b/outputs/stage_01/nsr10_spectra/data/case_01_nsr10_spectra.xlsx
@@ -37,13 +37,13 @@
         <v>0.0</v>
       </c>
       <c r="B2">
-        <v>0.17609374999999997</v>
+        <v>0.14087499999999997</v>
       </c>
       <c r="C2">
-        <v>0.5031249999999999</v>
+        <v>0.40249999999999997</v>
       </c>
       <c r="D2">
-        <v>0.7546875</v>
+        <v>0.60375</v>
       </c>
     </row>
     <row r="3">
@@ -51,13 +51,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.19694014246323527</v>
+        <v>0.15755211397058821</v>
       </c>
       <c r="C3">
-        <v>0.5626861213235294</v>
+        <v>0.4501488970588235</v>
       </c>
       <c r="D3">
-        <v>0.8440291819852941</v>
+        <v>0.6752233455882353</v>
       </c>
     </row>
     <row r="4">
@@ -65,13 +65,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.21778653492647052</v>
+        <v>0.17422922794117643</v>
       </c>
       <c r="C4">
-        <v>0.6222472426470587</v>
+        <v>0.49779779411764696</v>
       </c>
       <c r="D4">
-        <v>0.933370863970588</v>
+        <v>0.7466966911764704</v>
       </c>
     </row>
     <row r="5">
@@ -79,13 +79,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.23863292738970582</v>
+        <v>0.19090634191176467</v>
       </c>
       <c r="C5">
-        <v>0.6818083639705881</v>
+        <v>0.5454466911764705</v>
       </c>
       <c r="D5">
-        <v>1.0227125459558821</v>
+        <v>0.8181700367647058</v>
       </c>
     </row>
     <row r="6">
@@ -93,13 +93,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.2594793198529411</v>
+        <v>0.20758345588235289</v>
       </c>
       <c r="C6">
-        <v>0.7413694852941175</v>
+        <v>0.593095588235294</v>
       </c>
       <c r="D6">
-        <v>1.1120542279411763</v>
+        <v>0.8896433823529409</v>
       </c>
     </row>
     <row r="7">
@@ -107,13 +107,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.28032571231617637</v>
+        <v>0.22426056985294113</v>
       </c>
       <c r="C7">
-        <v>0.8009306066176468</v>
+        <v>0.6407444852941175</v>
       </c>
       <c r="D7">
-        <v>1.2013959099264702</v>
+        <v>0.9611167279411763</v>
       </c>
     </row>
     <row r="8">
@@ -121,13 +121,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.30117210477941164</v>
+        <v>0.24093768382352934</v>
       </c>
       <c r="C8">
-        <v>0.8604917279411762</v>
+        <v>0.688393382352941</v>
       </c>
       <c r="D8">
-        <v>1.2907375919117643</v>
+        <v>1.0325900735294116</v>
       </c>
     </row>
     <row r="9">
@@ -135,13 +135,13 @@
         <v>0.07</v>
       </c>
       <c r="B9">
-        <v>0.322018497242647</v>
+        <v>0.2576147977941176</v>
       </c>
       <c r="C9">
-        <v>0.9200528492647057</v>
+        <v>0.7360422794117646</v>
       </c>
       <c r="D9">
-        <v>1.3800792738970584</v>
+        <v>1.1040634191176468</v>
       </c>
     </row>
     <row r="10">
@@ -149,13 +149,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.34286488970588225</v>
+        <v>0.27429191176470585</v>
       </c>
       <c r="C10">
-        <v>0.9796139705882351</v>
+        <v>0.7836911764705882</v>
       </c>
       <c r="D10">
-        <v>1.4694209558823526</v>
+        <v>1.1755367647058823</v>
       </c>
     </row>
     <row r="11">
@@ -163,13 +163,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.3637112821691175</v>
+        <v>0.29096902573529404</v>
       </c>
       <c r="C11">
-        <v>1.0391750919117644</v>
+        <v>0.8313400735294115</v>
       </c>
       <c r="D11">
-        <v>1.5587626378676465</v>
+        <v>1.2470101102941173</v>
       </c>
     </row>
     <row r="12">
@@ -177,13 +177,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.3845576746323528</v>
+        <v>0.3076461397058823</v>
       </c>
       <c r="C12">
-        <v>1.0987362132352938</v>
+        <v>0.8789889705882351</v>
       </c>
       <c r="D12">
-        <v>1.6481043198529406</v>
+        <v>1.3184834558823526</v>
       </c>
     </row>
     <row r="13">
@@ -191,13 +191,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.4054040670955881</v>
+        <v>0.32432325367647047</v>
       </c>
       <c r="C13">
-        <v>1.1582973345588232</v>
+        <v>0.9266378676470586</v>
       </c>
       <c r="D13">
-        <v>1.7374460018382347</v>
+        <v>1.3899568014705879</v>
       </c>
     </row>
     <row r="14">
@@ -205,13 +205,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.42625045955882335</v>
+        <v>0.3410003676470587</v>
       </c>
       <c r="C14">
-        <v>1.2178584558823524</v>
+        <v>0.974286764705882</v>
       </c>
       <c r="D14">
-        <v>1.8267876838235286</v>
+        <v>1.4614301470588231</v>
       </c>
     </row>
     <row r="15">
@@ -219,13 +219,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C15">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D15">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="16">
@@ -233,13 +233,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C16">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D16">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="17">
@@ -247,13 +247,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C17">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D17">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="18">
@@ -261,13 +261,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C18">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D18">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="19">
@@ -275,13 +275,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C19">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D19">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="20">
@@ -289,13 +289,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C20">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D20">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="21">
@@ -303,13 +303,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C21">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D21">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="22">
@@ -317,13 +317,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C22">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D22">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="23">
@@ -331,13 +331,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C23">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D23">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="24">
@@ -345,13 +345,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C24">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D24">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="25">
@@ -359,13 +359,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C25">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D25">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="26">
@@ -373,13 +373,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C26">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D26">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="27">
@@ -387,13 +387,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C27">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D27">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="28">
@@ -401,13 +401,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C28">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D28">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="29">
@@ -415,13 +415,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C29">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D29">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="30">
@@ -429,13 +429,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C30">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D30">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="31">
@@ -443,13 +443,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C31">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D31">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="32">
@@ -457,13 +457,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C32">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D32">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="33">
@@ -471,13 +471,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C33">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D33">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="34">
@@ -485,13 +485,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C34">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D34">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="35">
@@ -499,13 +499,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C35">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D35">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="36">
@@ -513,13 +513,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C36">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D36">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="37">
@@ -527,13 +527,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C37">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D37">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="38">
@@ -541,13 +541,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C38">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D38">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="39">
@@ -555,13 +555,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C39">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D39">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="40">
@@ -569,13 +569,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C40">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D40">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="41">
@@ -583,13 +583,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C41">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D41">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="42">
@@ -597,13 +597,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C42">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D42">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="43">
@@ -611,13 +611,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C43">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D43">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="44">
@@ -625,13 +625,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C44">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D44">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="45">
@@ -639,13 +639,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C45">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D45">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="46">
@@ -653,13 +653,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C46">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D46">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="47">
@@ -667,13 +667,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C47">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D47">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="48">
@@ -681,13 +681,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C48">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D48">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="49">
@@ -695,13 +695,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C49">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D49">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="50">
@@ -709,13 +709,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C50">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D50">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="51">
@@ -723,13 +723,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C51">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D51">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="52">
@@ -737,13 +737,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C52">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D52">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="53">
@@ -751,13 +751,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C53">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D53">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="54">
@@ -765,13 +765,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C54">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D54">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="55">
@@ -779,13 +779,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C55">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D55">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="56">
@@ -793,13 +793,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C56">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D56">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="57">
@@ -807,13 +807,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C57">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D57">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="58">
@@ -821,13 +821,13 @@
         <v>0.56</v>
       </c>
       <c r="B58">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C58">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D58">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="59">
@@ -835,13 +835,13 @@
         <v>0.57</v>
       </c>
       <c r="B59">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C59">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D59">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="60">
@@ -849,13 +849,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C60">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D60">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="61">
@@ -863,13 +863,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C61">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D61">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="62">
@@ -877,13 +877,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.4402343749999999</v>
+        <v>0.35218749999999993</v>
       </c>
       <c r="C62">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="D62">
-        <v>1.8867187499999996</v>
+        <v>1.509375</v>
       </c>
     </row>
     <row r="63">
@@ -891,13 +891,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.4389344262295081</v>
+        <v>0.3511475409836065</v>
       </c>
       <c r="C63">
-        <v>1.2540983606557377</v>
+        <v>1.0032786885245901</v>
       </c>
       <c r="D63">
-        <v>1.8811475409836065</v>
+        <v>1.5049180327868852</v>
       </c>
     </row>
     <row r="64">
@@ -905,13 +905,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.4318548387096774</v>
+        <v>0.3454838709677419</v>
       </c>
       <c r="C64">
-        <v>1.2338709677419355</v>
+        <v>0.9870967741935484</v>
       </c>
       <c r="D64">
-        <v>1.8508064516129032</v>
+        <v>1.4806451612903224</v>
       </c>
     </row>
     <row r="65">
@@ -919,13 +919,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.42499999999999993</v>
+        <v>0.33999999999999997</v>
       </c>
       <c r="C65">
-        <v>1.2142857142857142</v>
+        <v>0.9714285714285714</v>
       </c>
       <c r="D65">
-        <v>1.8214285714285712</v>
+        <v>1.457142857142857</v>
       </c>
     </row>
     <row r="66">
@@ -933,13 +933,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.418359375</v>
+        <v>0.33468749999999997</v>
       </c>
       <c r="C66">
-        <v>1.1953125</v>
+        <v>0.9562499999999999</v>
       </c>
       <c r="D66">
-        <v>1.79296875</v>
+        <v>1.434375</v>
       </c>
     </row>
     <row r="67">
@@ -947,13 +947,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.4119230769230769</v>
+        <v>0.3295384615384615</v>
       </c>
       <c r="C67">
-        <v>1.176923076923077</v>
+        <v>0.9415384615384614</v>
       </c>
       <c r="D67">
-        <v>1.7653846153846153</v>
+        <v>1.4123076923076923</v>
       </c>
     </row>
     <row r="68">
@@ -961,13 +961,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.4056818181818181</v>
+        <v>0.3245454545454545</v>
       </c>
       <c r="C68">
-        <v>1.159090909090909</v>
+        <v>0.9272727272727272</v>
       </c>
       <c r="D68">
-        <v>1.7386363636363633</v>
+        <v>1.3909090909090909</v>
       </c>
     </row>
     <row r="69">
@@ -975,13 +975,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.39962686567164174</v>
+        <v>0.3197014925373134</v>
       </c>
       <c r="C69">
-        <v>1.1417910447761193</v>
+        <v>0.9134328358208954</v>
       </c>
       <c r="D69">
-        <v>1.7126865671641789</v>
+        <v>1.370149253731343</v>
       </c>
     </row>
     <row r="70">
@@ -989,13 +989,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.39375</v>
+        <v>0.31499999999999995</v>
       </c>
       <c r="C70">
-        <v>1.125</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="D70">
-        <v>1.6875</v>
+        <v>1.3499999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -1003,13 +1003,13 @@
         <v>0.69</v>
       </c>
       <c r="B71">
-        <v>0.38804347826086955</v>
+        <v>0.31043478260869567</v>
       </c>
       <c r="C71">
-        <v>1.108695652173913</v>
+        <v>0.8869565217391305</v>
       </c>
       <c r="D71">
-        <v>1.6630434782608696</v>
+        <v>1.3304347826086957</v>
       </c>
     </row>
     <row r="72">
@@ -1017,13 +1017,13 @@
         <v>0.7</v>
       </c>
       <c r="B72">
-        <v>0.3825</v>
+        <v>0.306</v>
       </c>
       <c r="C72">
-        <v>1.092857142857143</v>
+        <v>0.8742857142857143</v>
       </c>
       <c r="D72">
-        <v>1.6392857142857145</v>
+        <v>1.3114285714285714</v>
       </c>
     </row>
     <row r="73">
@@ -1031,13 +1031,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.377112676056338</v>
+        <v>0.30169014084507045</v>
       </c>
       <c r="C73">
-        <v>1.0774647887323945</v>
+        <v>0.8619718309859156</v>
       </c>
       <c r="D73">
-        <v>1.6161971830985917</v>
+        <v>1.2929577464788733</v>
       </c>
     </row>
     <row r="74">
@@ -1045,13 +1045,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.37187499999999996</v>
+        <v>0.2975</v>
       </c>
       <c r="C74">
-        <v>1.0625</v>
+        <v>0.85</v>
       </c>
       <c r="D74">
-        <v>1.59375</v>
+        <v>1.275</v>
       </c>
     </row>
     <row r="75">
@@ -1059,13 +1059,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.3667808219178082</v>
+        <v>0.29342465753424657</v>
       </c>
       <c r="C75">
-        <v>1.047945205479452</v>
+        <v>0.8383561643835616</v>
       </c>
       <c r="D75">
-        <v>1.571917808219178</v>
+        <v>1.2575342465753425</v>
       </c>
     </row>
     <row r="76">
@@ -1073,13 +1073,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.3618243243243243</v>
+        <v>0.28945945945945944</v>
       </c>
       <c r="C76">
-        <v>1.0337837837837838</v>
+        <v>0.827027027027027</v>
       </c>
       <c r="D76">
-        <v>1.5506756756756757</v>
+        <v>1.2405405405405405</v>
       </c>
     </row>
     <row r="77">
@@ -1087,13 +1087,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.357</v>
+        <v>0.28559999999999997</v>
       </c>
       <c r="C77">
-        <v>1.02</v>
+        <v>0.816</v>
       </c>
       <c r="D77">
-        <v>1.53</v>
+        <v>1.224</v>
       </c>
     </row>
     <row r="78">
@@ -1101,13 +1101,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.3523026315789473</v>
+        <v>0.28184210526315784</v>
       </c>
       <c r="C78">
-        <v>1.006578947368421</v>
+        <v>0.8052631578947368</v>
       </c>
       <c r="D78">
-        <v>1.5098684210526314</v>
+        <v>1.2078947368421051</v>
       </c>
     </row>
     <row r="79">
@@ -1115,13 +1115,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.34772727272727266</v>
+        <v>0.27818181818181814</v>
       </c>
       <c r="C79">
-        <v>0.9935064935064934</v>
+        <v>0.7948051948051947</v>
       </c>
       <c r="D79">
-        <v>1.4902597402597402</v>
+        <v>1.192207792207792</v>
       </c>
     </row>
     <row r="80">
@@ -1129,13 +1129,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.3432692307692307</v>
+        <v>0.2746153846153846</v>
       </c>
       <c r="C80">
-        <v>0.9807692307692307</v>
+        <v>0.7846153846153846</v>
       </c>
       <c r="D80">
-        <v>1.471153846153846</v>
+        <v>1.176923076923077</v>
       </c>
     </row>
     <row r="81">
@@ -1143,13 +1143,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.33892405063291137</v>
+        <v>0.27113924050632904</v>
       </c>
       <c r="C81">
-        <v>0.9683544303797468</v>
+        <v>0.7746835443037974</v>
       </c>
       <c r="D81">
-        <v>1.4525316455696202</v>
+        <v>1.1620253164556962</v>
       </c>
     </row>
     <row r="82">
@@ -1157,13 +1157,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.33468749999999997</v>
+        <v>0.26774999999999993</v>
       </c>
       <c r="C82">
-        <v>0.9562499999999999</v>
+        <v>0.7649999999999999</v>
       </c>
       <c r="D82">
-        <v>1.434375</v>
+        <v>1.1475</v>
       </c>
     </row>
     <row r="83">
@@ -1171,13 +1171,13 @@
         <v>0.81</v>
       </c>
       <c r="B83">
-        <v>0.33055555555555555</v>
+        <v>0.2644444444444444</v>
       </c>
       <c r="C83">
-        <v>0.9444444444444444</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="D83">
-        <v>1.4166666666666665</v>
+        <v>1.1333333333333333</v>
       </c>
     </row>
     <row r="84">
@@ -1185,13 +1185,13 @@
         <v>0.82</v>
       </c>
       <c r="B84">
-        <v>0.32652439024390245</v>
+        <v>0.26121951219512196</v>
       </c>
       <c r="C84">
-        <v>0.9329268292682927</v>
+        <v>0.7463414634146341</v>
       </c>
       <c r="D84">
-        <v>1.399390243902439</v>
+        <v>1.1195121951219513</v>
       </c>
     </row>
     <row r="85">
@@ -1199,13 +1199,13 @@
         <v>0.83</v>
       </c>
       <c r="B85">
-        <v>0.3225903614457831</v>
+        <v>0.2580722891566265</v>
       </c>
       <c r="C85">
-        <v>0.9216867469879518</v>
+        <v>0.7373493975903614</v>
       </c>
       <c r="D85">
-        <v>1.3825301204819278</v>
+        <v>1.106024096385542</v>
       </c>
     </row>
     <row r="86">
@@ -1213,13 +1213,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.31875000000000003</v>
+        <v>0.25499999999999995</v>
       </c>
       <c r="C86">
-        <v>0.9107142857142858</v>
+        <v>0.7285714285714285</v>
       </c>
       <c r="D86">
-        <v>1.3660714285714288</v>
+        <v>1.0928571428571427</v>
       </c>
     </row>
     <row r="87">
@@ -1227,13 +1227,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.315</v>
+        <v>0.252</v>
       </c>
       <c r="C87">
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
       <c r="D87">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="88">
@@ -1241,13 +1241,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.31133720930232556</v>
+        <v>0.24906976744186043</v>
       </c>
       <c r="C88">
-        <v>0.8895348837209303</v>
+        <v>0.7116279069767442</v>
       </c>
       <c r="D88">
-        <v>1.3343023255813953</v>
+        <v>1.0674418604651161</v>
       </c>
     </row>
     <row r="89">
@@ -1255,13 +1255,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.30775862068965515</v>
+        <v>0.24620689655172412</v>
       </c>
       <c r="C89">
-        <v>0.8793103448275862</v>
+        <v>0.7034482758620689</v>
       </c>
       <c r="D89">
-        <v>1.3189655172413792</v>
+        <v>1.0551724137931033</v>
       </c>
     </row>
     <row r="90">
@@ -1269,13 +1269,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.30426136363636364</v>
+        <v>0.24340909090909088</v>
       </c>
       <c r="C90">
-        <v>0.8693181818181819</v>
+        <v>0.6954545454545454</v>
       </c>
       <c r="D90">
-        <v>1.303977272727273</v>
+        <v>1.0431818181818182</v>
       </c>
     </row>
     <row r="91">
@@ -1283,13 +1283,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.3008426966292135</v>
+        <v>0.24067415730337077</v>
       </c>
       <c r="C91">
-        <v>0.8595505617977528</v>
+        <v>0.6876404494382022</v>
       </c>
       <c r="D91">
-        <v>1.2893258426966292</v>
+        <v>1.0314606741573034</v>
       </c>
     </row>
     <row r="92">
@@ -1297,13 +1297,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2975</v>
+        <v>0.23799999999999996</v>
       </c>
       <c r="C92">
-        <v>0.85</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="D92">
-        <v>1.275</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="93">
@@ -1311,13 +1311,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.29423076923076924</v>
+        <v>0.23538461538461536</v>
       </c>
       <c r="C93">
-        <v>0.8406593406593407</v>
+        <v>0.6725274725274725</v>
       </c>
       <c r="D93">
-        <v>1.260989010989011</v>
+        <v>1.0087912087912088</v>
       </c>
     </row>
     <row r="94">
@@ -1325,13 +1325,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2910326086956522</v>
+        <v>0.2328260869565217</v>
       </c>
       <c r="C94">
-        <v>0.8315217391304348</v>
+        <v>0.6652173913043478</v>
       </c>
       <c r="D94">
-        <v>1.2472826086956523</v>
+        <v>0.9978260869565216</v>
       </c>
     </row>
     <row r="95">
@@ -1339,13 +1339,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.28790322580645156</v>
+        <v>0.23032258064516123</v>
       </c>
       <c r="C95">
-        <v>0.8225806451612903</v>
+        <v>0.6580645161290322</v>
       </c>
       <c r="D95">
-        <v>1.2338709677419355</v>
+        <v>0.9870967741935482</v>
       </c>
     </row>
     <row r="96">
@@ -1353,13 +1353,13 @@
         <v>0.94</v>
       </c>
       <c r="B96">
-        <v>0.2848404255319149</v>
+        <v>0.22787234042553192</v>
       </c>
       <c r="C96">
-        <v>0.8138297872340426</v>
+        <v>0.6510638297872341</v>
       </c>
       <c r="D96">
-        <v>1.220744680851064</v>
+        <v>0.9765957446808511</v>
       </c>
     </row>
     <row r="97">
@@ -1367,13 +1367,13 @@
         <v>0.95</v>
       </c>
       <c r="B97">
-        <v>0.2818421052631579</v>
+        <v>0.2254736842105263</v>
       </c>
       <c r="C97">
-        <v>0.8052631578947369</v>
+        <v>0.6442105263157895</v>
       </c>
       <c r="D97">
-        <v>1.2078947368421054</v>
+        <v>0.9663157894736842</v>
       </c>
     </row>
     <row r="98">
@@ -1381,13 +1381,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.27890624999999997</v>
+        <v>0.22312500000000002</v>
       </c>
       <c r="C98">
-        <v>0.796875</v>
+        <v>0.6375000000000001</v>
       </c>
       <c r="D98">
-        <v>1.1953125</v>
+        <v>0.95625</v>
       </c>
     </row>
     <row r="99">
@@ -1395,13 +1395,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.27603092783505156</v>
+        <v>0.22082474226804122</v>
       </c>
       <c r="C99">
-        <v>0.7886597938144331</v>
+        <v>0.6309278350515464</v>
       </c>
       <c r="D99">
-        <v>1.1829896907216497</v>
+        <v>0.9463917525773196</v>
       </c>
     </row>
     <row r="100">
@@ -1409,13 +1409,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2732142857142857</v>
+        <v>0.21857142857142858</v>
       </c>
       <c r="C100">
-        <v>0.7806122448979592</v>
+        <v>0.6244897959183674</v>
       </c>
       <c r="D100">
-        <v>1.1709183673469388</v>
+        <v>0.9367346938775512</v>
       </c>
     </row>
     <row r="101">
@@ -1423,13 +1423,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.27045454545454545</v>
+        <v>0.21636363636363634</v>
       </c>
       <c r="C101">
-        <v>0.7727272727272727</v>
+        <v>0.6181818181818182</v>
       </c>
       <c r="D101">
-        <v>1.1590909090909092</v>
+        <v>0.9272727272727272</v>
       </c>
     </row>
     <row r="102">
@@ -1437,13 +1437,13 @@
         <v>1.0</v>
       </c>
       <c r="B102">
-        <v>0.26775</v>
+        <v>0.21419999999999997</v>
       </c>
       <c r="C102">
-        <v>0.765</v>
+        <v>0.612</v>
       </c>
       <c r="D102">
-        <v>1.1475</v>
+        <v>0.9179999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -1451,13 +1451,13 @@
         <v>1.01</v>
       </c>
       <c r="B103">
-        <v>0.26509900990099006</v>
+        <v>0.21207920792079207</v>
       </c>
       <c r="C103">
-        <v>0.7574257425742574</v>
+        <v>0.6059405940594059</v>
       </c>
       <c r="D103">
-        <v>1.136138613861386</v>
+        <v>0.9089108910891088</v>
       </c>
     </row>
     <row r="104">
@@ -1465,13 +1465,13 @@
         <v>1.02</v>
       </c>
       <c r="B104">
-        <v>0.26249999999999996</v>
+        <v>0.21</v>
       </c>
       <c r="C104">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D104">
-        <v>1.125</v>
+        <v>0.8999999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -1479,13 +1479,13 @@
         <v>1.03</v>
       </c>
       <c r="B105">
-        <v>0.2599514563106796</v>
+        <v>0.20796116504854364</v>
       </c>
       <c r="C105">
-        <v>0.7427184466019418</v>
+        <v>0.5941747572815533</v>
       </c>
       <c r="D105">
-        <v>1.1140776699029127</v>
+        <v>0.8912621359223301</v>
       </c>
     </row>
     <row r="106">
@@ -1493,13 +1493,13 @@
         <v>1.04</v>
       </c>
       <c r="B106">
-        <v>0.25745192307692305</v>
+        <v>0.20596153846153845</v>
       </c>
       <c r="C106">
-        <v>0.735576923076923</v>
+        <v>0.5884615384615385</v>
       </c>
       <c r="D106">
-        <v>1.1033653846153846</v>
+        <v>0.8826923076923077</v>
       </c>
     </row>
     <row r="107">
@@ -1507,13 +1507,13 @@
         <v>1.05</v>
       </c>
       <c r="B107">
-        <v>0.25499999999999995</v>
+        <v>0.204</v>
       </c>
       <c r="C107">
-        <v>0.7285714285714285</v>
+        <v>0.5828571428571429</v>
       </c>
       <c r="D107">
-        <v>1.0928571428571427</v>
+        <v>0.8742857142857143</v>
       </c>
     </row>
     <row r="108">
@@ -1521,13 +1521,13 @@
         <v>1.06</v>
       </c>
       <c r="B108">
-        <v>0.2525943396226415</v>
+        <v>0.20207547169811318</v>
       </c>
       <c r="C108">
-        <v>0.7216981132075472</v>
+        <v>0.5773584905660377</v>
       </c>
       <c r="D108">
-        <v>1.0825471698113207</v>
+        <v>0.8660377358490565</v>
       </c>
     </row>
     <row r="109">
@@ -1535,13 +1535,13 @@
         <v>1.07</v>
       </c>
       <c r="B109">
-        <v>0.2502336448598131</v>
+        <v>0.20018691588785045</v>
       </c>
       <c r="C109">
-        <v>0.7149532710280374</v>
+        <v>0.5719626168224299</v>
       </c>
       <c r="D109">
-        <v>1.0724299065420562</v>
+        <v>0.8579439252336448</v>
       </c>
     </row>
     <row r="110">
@@ -1549,13 +1549,13 @@
         <v>1.08</v>
       </c>
       <c r="B110">
-        <v>0.24791666666666662</v>
+        <v>0.1983333333333333</v>
       </c>
       <c r="C110">
-        <v>0.7083333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="D110">
-        <v>1.0625</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="111">
@@ -1563,13 +1563,13 @@
         <v>1.09</v>
       </c>
       <c r="B111">
-        <v>0.24564220183486238</v>
+        <v>0.19651376146788987</v>
       </c>
       <c r="C111">
-        <v>0.7018348623853211</v>
+        <v>0.5614678899082568</v>
       </c>
       <c r="D111">
-        <v>1.0527522935779816</v>
+        <v>0.8422018348623852</v>
       </c>
     </row>
     <row r="112">
@@ -1577,13 +1577,13 @@
         <v>1.1</v>
       </c>
       <c r="B112">
-        <v>0.24340909090909088</v>
+        <v>0.1947272727272727</v>
       </c>
       <c r="C112">
-        <v>0.6954545454545454</v>
+        <v>0.5563636363636363</v>
       </c>
       <c r="D112">
-        <v>1.0431818181818182</v>
+        <v>0.8345454545454545</v>
       </c>
     </row>
     <row r="113">
@@ -1591,13 +1591,13 @@
         <v>1.11</v>
       </c>
       <c r="B113">
-        <v>0.2412162162162162</v>
+        <v>0.19297297297297294</v>
       </c>
       <c r="C113">
-        <v>0.6891891891891891</v>
+        <v>0.5513513513513513</v>
       </c>
       <c r="D113">
-        <v>1.0337837837837838</v>
+        <v>0.8270270270270269</v>
       </c>
     </row>
     <row r="114">
@@ -1605,13 +1605,13 @@
         <v>1.12</v>
       </c>
       <c r="B114">
-        <v>0.23906249999999996</v>
+        <v>0.19124999999999998</v>
       </c>
       <c r="C114">
-        <v>0.6830357142857142</v>
+        <v>0.5464285714285714</v>
       </c>
       <c r="D114">
-        <v>1.0245535714285712</v>
+        <v>0.8196428571428571</v>
       </c>
     </row>
     <row r="115">
@@ -1619,13 +1619,13 @@
         <v>1.13</v>
       </c>
       <c r="B115">
-        <v>0.23694690265486726</v>
+        <v>0.1895575221238938</v>
       </c>
       <c r="C115">
-        <v>0.6769911504424779</v>
+        <v>0.5415929203539823</v>
       </c>
       <c r="D115">
-        <v>1.0154867256637168</v>
+        <v>0.8123893805309734</v>
       </c>
     </row>
     <row r="116">
@@ -1633,13 +1633,13 @@
         <v>1.14</v>
       </c>
       <c r="B116">
-        <v>0.2348684210526316</v>
+        <v>0.18789473684210525</v>
       </c>
       <c r="C116">
-        <v>0.6710526315789475</v>
+        <v>0.5368421052631579</v>
       </c>
       <c r="D116">
-        <v>1.0065789473684212</v>
+        <v>0.8052631578947369</v>
       </c>
     </row>
     <row r="117">
@@ -1647,13 +1647,13 @@
         <v>1.15</v>
       </c>
       <c r="B117">
-        <v>0.23282608695652174</v>
+        <v>0.1862608695652174</v>
       </c>
       <c r="C117">
-        <v>0.6652173913043479</v>
+        <v>0.5321739130434783</v>
       </c>
       <c r="D117">
-        <v>0.9978260869565219</v>
+        <v>0.7982608695652174</v>
       </c>
     </row>
     <row r="118">
@@ -1661,13 +1661,13 @@
         <v>1.16</v>
       </c>
       <c r="B118">
-        <v>0.23081896551724138</v>
+        <v>0.18465517241379312</v>
       </c>
       <c r="C118">
-        <v>0.6594827586206897</v>
+        <v>0.5275862068965518</v>
       </c>
       <c r="D118">
-        <v>0.9892241379310346</v>
+        <v>0.7913793103448277</v>
       </c>
     </row>
     <row r="119">
@@ -1675,13 +1675,13 @@
         <v>1.17</v>
       </c>
       <c r="B119">
-        <v>0.22884615384615384</v>
+        <v>0.18307692307692308</v>
       </c>
       <c r="C119">
-        <v>0.6538461538461539</v>
+        <v>0.5230769230769231</v>
       </c>
       <c r="D119">
-        <v>0.9807692307692308</v>
+        <v>0.7846153846153847</v>
       </c>
     </row>
     <row r="120">
@@ -1689,13 +1689,13 @@
         <v>1.18</v>
       </c>
       <c r="B120">
-        <v>0.22690677966101694</v>
+        <v>0.18152542372881356</v>
       </c>
       <c r="C120">
-        <v>0.6483050847457628</v>
+        <v>0.5186440677966102</v>
       </c>
       <c r="D120">
-        <v>0.9724576271186441</v>
+        <v>0.7779661016949153</v>
       </c>
     </row>
     <row r="121">
@@ -1703,13 +1703,13 @@
         <v>1.19</v>
       </c>
       <c r="B121">
-        <v>0.225</v>
+        <v>0.18000000000000002</v>
       </c>
       <c r="C121">
-        <v>0.6428571428571429</v>
+        <v>0.5142857142857143</v>
       </c>
       <c r="D121">
-        <v>0.9642857142857144</v>
+        <v>0.7714285714285716</v>
       </c>
     </row>
     <row r="122">
@@ -1717,13 +1717,13 @@
         <v>1.2</v>
       </c>
       <c r="B122">
-        <v>0.22312500000000002</v>
+        <v>0.1785</v>
       </c>
       <c r="C122">
-        <v>0.6375000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="D122">
-        <v>0.95625</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="123">
@@ -1731,13 +1731,13 @@
         <v>1.21</v>
       </c>
       <c r="B123">
-        <v>0.22128099173553717</v>
+        <v>0.17702479338842975</v>
       </c>
       <c r="C123">
-        <v>0.6322314049586777</v>
+        <v>0.5057851239669422</v>
       </c>
       <c r="D123">
-        <v>0.9483471074380165</v>
+        <v>0.7586776859504133</v>
       </c>
     </row>
     <row r="124">
@@ -1745,13 +1745,13 @@
         <v>1.22</v>
       </c>
       <c r="B124">
-        <v>0.21946721311475406</v>
+        <v>0.17557377049180325</v>
       </c>
       <c r="C124">
-        <v>0.6270491803278688</v>
+        <v>0.5016393442622951</v>
       </c>
       <c r="D124">
-        <v>0.9405737704918032</v>
+        <v>0.7524590163934426</v>
       </c>
     </row>
     <row r="125">
@@ -1759,13 +1759,13 @@
         <v>1.23</v>
       </c>
       <c r="B125">
-        <v>0.2176829268292683</v>
+        <v>0.17414634146341462</v>
       </c>
       <c r="C125">
-        <v>0.6219512195121951</v>
+        <v>0.4975609756097561</v>
       </c>
       <c r="D125">
-        <v>0.9329268292682926</v>
+        <v>0.7463414634146341</v>
       </c>
     </row>
     <row r="126">
@@ -1773,13 +1773,13 @@
         <v>1.24</v>
       </c>
       <c r="B126">
-        <v>0.2159274193548387</v>
+        <v>0.17274193548387096</v>
       </c>
       <c r="C126">
-        <v>0.6169354838709677</v>
+        <v>0.4935483870967742</v>
       </c>
       <c r="D126">
-        <v>0.9254032258064516</v>
+        <v>0.7403225806451612</v>
       </c>
     </row>
     <row r="127">
@@ -1787,13 +1787,13 @@
         <v>1.25</v>
       </c>
       <c r="B127">
-        <v>0.21419999999999997</v>
+        <v>0.17135999999999998</v>
       </c>
       <c r="C127">
-        <v>0.612</v>
+        <v>0.4896</v>
       </c>
       <c r="D127">
-        <v>0.9179999999999999</v>
+        <v>0.7343999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -1801,13 +1801,13 @@
         <v>1.26</v>
       </c>
       <c r="B128">
-        <v>0.21249999999999997</v>
+        <v>0.16999999999999998</v>
       </c>
       <c r="C128">
-        <v>0.6071428571428571</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="D128">
-        <v>0.9107142857142856</v>
+        <v>0.7285714285714285</v>
       </c>
     </row>
     <row r="129">
@@ -1815,13 +1815,13 @@
         <v>1.27</v>
       </c>
       <c r="B129">
-        <v>0.2108267716535433</v>
+        <v>0.16866141732283463</v>
       </c>
       <c r="C129">
-        <v>0.6023622047244095</v>
+        <v>0.4818897637795275</v>
       </c>
       <c r="D129">
-        <v>0.9035433070866142</v>
+        <v>0.7228346456692913</v>
       </c>
     </row>
     <row r="130">
@@ -1829,13 +1829,13 @@
         <v>1.28</v>
       </c>
       <c r="B130">
-        <v>0.2091796875</v>
+        <v>0.16734374999999999</v>
       </c>
       <c r="C130">
-        <v>0.59765625</v>
+        <v>0.47812499999999997</v>
       </c>
       <c r="D130">
-        <v>0.896484375</v>
+        <v>0.7171875</v>
       </c>
     </row>
     <row r="131">
@@ -1843,13 +1843,13 @@
         <v>1.29</v>
       </c>
       <c r="B131">
-        <v>0.2075581395348837</v>
+        <v>0.16604651162790696</v>
       </c>
       <c r="C131">
-        <v>0.5930232558139534</v>
+        <v>0.47441860465116276</v>
       </c>
       <c r="D131">
-        <v>0.8895348837209301</v>
+        <v>0.7116279069767442</v>
       </c>
     </row>
     <row r="132">
@@ -1857,13 +1857,13 @@
         <v>1.3</v>
       </c>
       <c r="B132">
-        <v>0.20596153846153845</v>
+        <v>0.16476923076923075</v>
       </c>
       <c r="C132">
-        <v>0.5884615384615385</v>
+        <v>0.4707692307692307</v>
       </c>
       <c r="D132">
-        <v>0.8826923076923077</v>
+        <v>0.7061538461538461</v>
       </c>
     </row>
     <row r="133">
@@ -1871,13 +1871,13 @@
         <v>1.31</v>
       </c>
       <c r="B133">
-        <v>0.20438931297709922</v>
+        <v>0.16351145038167936</v>
       </c>
       <c r="C133">
-        <v>0.583969465648855</v>
+        <v>0.4671755725190839</v>
       </c>
       <c r="D133">
-        <v>0.8759541984732825</v>
+        <v>0.7007633587786259</v>
       </c>
     </row>
     <row r="134">
@@ -1885,13 +1885,13 @@
         <v>1.32</v>
       </c>
       <c r="B134">
-        <v>0.20284090909090904</v>
+        <v>0.16227272727272726</v>
       </c>
       <c r="C134">
-        <v>0.5795454545454545</v>
+        <v>0.4636363636363636</v>
       </c>
       <c r="D134">
-        <v>0.8693181818181817</v>
+        <v>0.6954545454545454</v>
       </c>
     </row>
     <row r="135">
@@ -1899,13 +1899,13 @@
         <v>1.33</v>
       </c>
       <c r="B135">
-        <v>0.2013157894736842</v>
+        <v>0.16105263157894734</v>
       </c>
       <c r="C135">
-        <v>0.575187969924812</v>
+        <v>0.4601503759398496</v>
       </c>
       <c r="D135">
-        <v>0.862781954887218</v>
+        <v>0.6902255639097744</v>
       </c>
     </row>
     <row r="136">
@@ -1913,13 +1913,13 @@
         <v>1.34</v>
       </c>
       <c r="B136">
-        <v>0.19981343283582087</v>
+        <v>0.1598507462686567</v>
       </c>
       <c r="C136">
-        <v>0.5708955223880596</v>
+        <v>0.4567164179104477</v>
       </c>
       <c r="D136">
-        <v>0.8563432835820894</v>
+        <v>0.6850746268656716</v>
       </c>
     </row>
     <row r="137">
@@ -1927,13 +1927,13 @@
         <v>1.35</v>
       </c>
       <c r="B137">
-        <v>0.1983333333333333</v>
+        <v>0.15866666666666665</v>
       </c>
       <c r="C137">
-        <v>0.5666666666666667</v>
+        <v>0.4533333333333333</v>
       </c>
       <c r="D137">
-        <v>0.85</v>
+        <v>0.6799999999999999</v>
       </c>
     </row>
     <row r="138">
@@ -1941,13 +1941,13 @@
         <v>1.36</v>
       </c>
       <c r="B138">
-        <v>0.196875</v>
+        <v>0.15749999999999997</v>
       </c>
       <c r="C138">
-        <v>0.5625</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="D138">
-        <v>0.84375</v>
+        <v>0.6749999999999999</v>
       </c>
     </row>
     <row r="139">
@@ -1955,13 +1955,13 @@
         <v>1.37</v>
       </c>
       <c r="B139">
-        <v>0.19543795620437954</v>
+        <v>0.15635036496350363</v>
       </c>
       <c r="C139">
-        <v>0.5583941605839415</v>
+        <v>0.4467153284671532</v>
       </c>
       <c r="D139">
-        <v>0.8375912408759123</v>
+        <v>0.6700729927007298</v>
       </c>
     </row>
     <row r="140">
@@ -1969,13 +1969,13 @@
         <v>1.38</v>
       </c>
       <c r="B140">
-        <v>0.19402173913043477</v>
+        <v>0.15521739130434783</v>
       </c>
       <c r="C140">
-        <v>0.5543478260869565</v>
+        <v>0.44347826086956527</v>
       </c>
       <c r="D140">
-        <v>0.8315217391304348</v>
+        <v>0.6652173913043479</v>
       </c>
     </row>
     <row r="141">
@@ -1983,13 +1983,13 @@
         <v>1.39</v>
       </c>
       <c r="B141">
-        <v>0.19262589928057552</v>
+        <v>0.15410071942446044</v>
       </c>
       <c r="C141">
-        <v>0.5503597122302158</v>
+        <v>0.44028776978417267</v>
       </c>
       <c r="D141">
-        <v>0.8255395683453237</v>
+        <v>0.660431654676259</v>
       </c>
     </row>
     <row r="142">
@@ -1997,13 +1997,13 @@
         <v>1.4</v>
       </c>
       <c r="B142">
-        <v>0.19125</v>
+        <v>0.153</v>
       </c>
       <c r="C142">
-        <v>0.5464285714285715</v>
+        <v>0.43714285714285717</v>
       </c>
       <c r="D142">
-        <v>0.8196428571428572</v>
+        <v>0.6557142857142857</v>
       </c>
     </row>
     <row r="143">
@@ -2011,13 +2011,13 @@
         <v>1.41</v>
       </c>
       <c r="B143">
-        <v>0.1898936170212766</v>
+        <v>0.15191489361702126</v>
       </c>
       <c r="C143">
-        <v>0.5425531914893618</v>
+        <v>0.4340425531914894</v>
       </c>
       <c r="D143">
-        <v>0.8138297872340426</v>
+        <v>0.6510638297872341</v>
       </c>
     </row>
     <row r="144">
@@ -2025,13 +2025,13 @@
         <v>1.42</v>
       </c>
       <c r="B144">
-        <v>0.188556338028169</v>
+        <v>0.15084507042253523</v>
       </c>
       <c r="C144">
-        <v>0.5387323943661972</v>
+        <v>0.4309859154929578</v>
       </c>
       <c r="D144">
-        <v>0.8080985915492959</v>
+        <v>0.6464788732394366</v>
       </c>
     </row>
     <row r="145">
@@ -2039,13 +2039,13 @@
         <v>1.43</v>
       </c>
       <c r="B145">
-        <v>0.18723776223776223</v>
+        <v>0.1497902097902098</v>
       </c>
       <c r="C145">
-        <v>0.534965034965035</v>
+        <v>0.427972027972028</v>
       </c>
       <c r="D145">
-        <v>0.8024475524475525</v>
+        <v>0.641958041958042</v>
       </c>
     </row>
     <row r="146">
@@ -2053,13 +2053,13 @@
         <v>1.44</v>
       </c>
       <c r="B146">
-        <v>0.18593749999999998</v>
+        <v>0.14875</v>
       </c>
       <c r="C146">
-        <v>0.53125</v>
+        <v>0.425</v>
       </c>
       <c r="D146">
-        <v>0.796875</v>
+        <v>0.6375</v>
       </c>
     </row>
     <row r="147">
@@ -2067,13 +2067,13 @@
         <v>1.45</v>
       </c>
       <c r="B147">
-        <v>0.18465517241379312</v>
+        <v>0.14772413793103448</v>
       </c>
       <c r="C147">
-        <v>0.5275862068965518</v>
+        <v>0.4220689655172414</v>
       </c>
       <c r="D147">
-        <v>0.7913793103448277</v>
+        <v>0.6331034482758621</v>
       </c>
     </row>
     <row r="148">
@@ -2081,13 +2081,13 @@
         <v>1.46</v>
       </c>
       <c r="B148">
-        <v>0.1833904109589041</v>
+        <v>0.14671232876712328</v>
       </c>
       <c r="C148">
-        <v>0.523972602739726</v>
+        <v>0.4191780821917808</v>
       </c>
       <c r="D148">
-        <v>0.785958904109589</v>
+        <v>0.6287671232876713</v>
       </c>
     </row>
     <row r="149">
@@ -2095,13 +2095,13 @@
         <v>1.47</v>
       </c>
       <c r="B149">
-        <v>0.18214285714285713</v>
+        <v>0.1457142857142857</v>
       </c>
       <c r="C149">
-        <v>0.5204081632653061</v>
+        <v>0.4163265306122449</v>
       </c>
       <c r="D149">
-        <v>0.7806122448979592</v>
+        <v>0.6244897959183673</v>
       </c>
     </row>
     <row r="150">
@@ -2109,13 +2109,13 @@
         <v>1.48</v>
       </c>
       <c r="B150">
-        <v>0.18091216216216216</v>
+        <v>0.14472972972972972</v>
       </c>
       <c r="C150">
-        <v>0.5168918918918919</v>
+        <v>0.4135135135135135</v>
       </c>
       <c r="D150">
-        <v>0.7753378378378378</v>
+        <v>0.6202702702702703</v>
       </c>
     </row>
     <row r="151">
@@ -2123,13 +2123,13 @@
         <v>1.49</v>
       </c>
       <c r="B151">
-        <v>0.1796979865771812</v>
+        <v>0.14375838926174495</v>
       </c>
       <c r="C151">
-        <v>0.5134228187919463</v>
+        <v>0.41073825503355704</v>
       </c>
       <c r="D151">
-        <v>0.7701342281879194</v>
+        <v>0.6161073825503356</v>
       </c>
     </row>
     <row r="152">
@@ -2137,13 +2137,13 @@
         <v>1.5</v>
       </c>
       <c r="B152">
-        <v>0.1785</v>
+        <v>0.14279999999999998</v>
       </c>
       <c r="C152">
-        <v>0.51</v>
+        <v>0.408</v>
       </c>
       <c r="D152">
-        <v>0.765</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="153">
@@ -2151,13 +2151,13 @@
         <v>1.51</v>
       </c>
       <c r="B153">
-        <v>0.17731788079470198</v>
+        <v>0.14185430463576157</v>
       </c>
       <c r="C153">
-        <v>0.5066225165562914</v>
+        <v>0.4052980132450331</v>
       </c>
       <c r="D153">
-        <v>0.7599337748344371</v>
+        <v>0.6079470198675496</v>
       </c>
     </row>
     <row r="154">
@@ -2165,13 +2165,13 @@
         <v>1.52</v>
       </c>
       <c r="B154">
-        <v>0.17615131578947366</v>
+        <v>0.14092105263157892</v>
       </c>
       <c r="C154">
-        <v>0.5032894736842105</v>
+        <v>0.4026315789473684</v>
       </c>
       <c r="D154">
-        <v>0.7549342105263157</v>
+        <v>0.6039473684210526</v>
       </c>
     </row>
     <row r="155">
@@ -2179,13 +2179,13 @@
         <v>1.53</v>
       </c>
       <c r="B155">
-        <v>0.175</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="C155">
-        <v>0.5</v>
+        <v>0.39999999999999997</v>
       </c>
       <c r="D155">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="156">
@@ -2193,13 +2193,13 @@
         <v>1.54</v>
       </c>
       <c r="B156">
-        <v>0.17386363636363633</v>
+        <v>0.13909090909090907</v>
       </c>
       <c r="C156">
-        <v>0.4967532467532467</v>
+        <v>0.39740259740259737</v>
       </c>
       <c r="D156">
-        <v>0.7451298701298701</v>
+        <v>0.596103896103896</v>
       </c>
     </row>
     <row r="157">
@@ -2207,13 +2207,13 @@
         <v>1.55</v>
       </c>
       <c r="B157">
-        <v>0.17274193548387096</v>
+        <v>0.13819354838709677</v>
       </c>
       <c r="C157">
-        <v>0.4935483870967742</v>
+        <v>0.39483870967741935</v>
       </c>
       <c r="D157">
-        <v>0.7403225806451612</v>
+        <v>0.5922580645161291</v>
       </c>
     </row>
     <row r="158">
@@ -2221,13 +2221,13 @@
         <v>1.56</v>
       </c>
       <c r="B158">
-        <v>0.17163461538461536</v>
+        <v>0.1373076923076923</v>
       </c>
       <c r="C158">
-        <v>0.49038461538461536</v>
+        <v>0.3923076923076923</v>
       </c>
       <c r="D158">
-        <v>0.735576923076923</v>
+        <v>0.5884615384615385</v>
       </c>
     </row>
     <row r="159">
@@ -2235,13 +2235,13 @@
         <v>1.57</v>
       </c>
       <c r="B159">
-        <v>0.17054140127388534</v>
+        <v>0.13643312101910826</v>
       </c>
       <c r="C159">
-        <v>0.4872611464968153</v>
+        <v>0.3898089171974522</v>
       </c>
       <c r="D159">
-        <v>0.7308917197452229</v>
+        <v>0.5847133757961783</v>
       </c>
     </row>
     <row r="160">
@@ -2249,13 +2249,13 @@
         <v>1.58</v>
       </c>
       <c r="B160">
-        <v>0.16946202531645568</v>
+        <v>0.13556962025316452</v>
       </c>
       <c r="C160">
-        <v>0.4841772151898734</v>
+        <v>0.3873417721518987</v>
       </c>
       <c r="D160">
-        <v>0.7262658227848101</v>
+        <v>0.5810126582278481</v>
       </c>
     </row>
     <row r="161">
@@ -2263,13 +2263,13 @@
         <v>1.59</v>
       </c>
       <c r="B161">
-        <v>0.16839622641509433</v>
+        <v>0.13471698113207545</v>
       </c>
       <c r="C161">
-        <v>0.4811320754716981</v>
+        <v>0.38490566037735846</v>
       </c>
       <c r="D161">
-        <v>0.7216981132075472</v>
+        <v>0.5773584905660377</v>
       </c>
     </row>
     <row r="162">
@@ -2277,13 +2277,13 @@
         <v>1.6</v>
       </c>
       <c r="B162">
-        <v>0.16734374999999999</v>
+        <v>0.13387499999999997</v>
       </c>
       <c r="C162">
-        <v>0.47812499999999997</v>
+        <v>0.38249999999999995</v>
       </c>
       <c r="D162">
-        <v>0.7171875</v>
+        <v>0.57375</v>
       </c>
     </row>
     <row r="163">
@@ -2291,13 +2291,13 @@
         <v>1.61</v>
       </c>
       <c r="B163">
-        <v>0.16630434782608694</v>
+        <v>0.13304347826086954</v>
       </c>
       <c r="C163">
-        <v>0.47515527950310554</v>
+        <v>0.38012422360248443</v>
       </c>
       <c r="D163">
-        <v>0.7127329192546583</v>
+        <v>0.5701863354037267</v>
       </c>
     </row>
     <row r="164">
@@ -2305,13 +2305,13 @@
         <v>1.62</v>
       </c>
       <c r="B164">
-        <v>0.16527777777777777</v>
+        <v>0.1322222222222222</v>
       </c>
       <c r="C164">
-        <v>0.4722222222222222</v>
+        <v>0.37777777777777777</v>
       </c>
       <c r="D164">
-        <v>0.7083333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
     </row>
     <row r="165">
@@ -2319,13 +2319,13 @@
         <v>1.63</v>
       </c>
       <c r="B165">
-        <v>0.16426380368098162</v>
+        <v>0.13141104294478526</v>
       </c>
       <c r="C165">
-        <v>0.4693251533742332</v>
+        <v>0.3754601226993865</v>
       </c>
       <c r="D165">
-        <v>0.7039877300613497</v>
+        <v>0.5631901840490797</v>
       </c>
     </row>
     <row r="166">
@@ -2333,13 +2333,13 @@
         <v>1.64</v>
       </c>
       <c r="B166">
-        <v>0.16326219512195123</v>
+        <v>0.13060975609756098</v>
       </c>
       <c r="C166">
-        <v>0.46646341463414637</v>
+        <v>0.37317073170731707</v>
       </c>
       <c r="D166">
-        <v>0.6996951219512195</v>
+        <v>0.5597560975609757</v>
       </c>
     </row>
     <row r="167">
@@ -2347,13 +2347,13 @@
         <v>1.65</v>
       </c>
       <c r="B167">
-        <v>0.1622727272727273</v>
+        <v>0.1298181818181818</v>
       </c>
       <c r="C167">
-        <v>0.4636363636363637</v>
+        <v>0.3709090909090909</v>
       </c>
       <c r="D167">
-        <v>0.6954545454545455</v>
+        <v>0.5563636363636364</v>
       </c>
     </row>
     <row r="168">
@@ -2361,13 +2361,13 @@
         <v>1.66</v>
       </c>
       <c r="B168">
-        <v>0.16129518072289156</v>
+        <v>0.12903614457831325</v>
       </c>
       <c r="C168">
-        <v>0.4608433734939759</v>
+        <v>0.3686746987951807</v>
       </c>
       <c r="D168">
-        <v>0.6912650602409639</v>
+        <v>0.553012048192771</v>
       </c>
     </row>
     <row r="169">
@@ -2375,13 +2375,13 @@
         <v>1.67</v>
       </c>
       <c r="B169">
-        <v>0.16032934131736526</v>
+        <v>0.1282634730538922</v>
       </c>
       <c r="C169">
-        <v>0.45808383233532934</v>
+        <v>0.3664670658682635</v>
       </c>
       <c r="D169">
-        <v>0.687125748502994</v>
+        <v>0.5497005988023953</v>
       </c>
     </row>
     <row r="170">
@@ -2389,13 +2389,13 @@
         <v>1.68</v>
       </c>
       <c r="B170">
-        <v>0.15937500000000002</v>
+        <v>0.12749999999999997</v>
       </c>
       <c r="C170">
-        <v>0.4553571428571429</v>
+        <v>0.36428571428571427</v>
       </c>
       <c r="D170">
-        <v>0.6830357142857144</v>
+        <v>0.5464285714285714</v>
       </c>
     </row>
     <row r="171">
@@ -2403,13 +2403,13 @@
         <v>1.69</v>
       </c>
       <c r="B171">
-        <v>0.1584319526627219</v>
+        <v>0.1267455621301775</v>
       </c>
       <c r="C171">
-        <v>0.45266272189349116</v>
+        <v>0.36213017751479293</v>
       </c>
       <c r="D171">
-        <v>0.6789940828402368</v>
+        <v>0.5431952662721894</v>
       </c>
     </row>
     <row r="172">
@@ -2417,13 +2417,13 @@
         <v>1.7</v>
       </c>
       <c r="B172">
-        <v>0.1575</v>
+        <v>0.126</v>
       </c>
       <c r="C172">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="D172">
-        <v>0.675</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="173">
@@ -2431,13 +2431,13 @@
         <v>1.71</v>
       </c>
       <c r="B173">
-        <v>0.15657894736842104</v>
+        <v>0.12526315789473683</v>
       </c>
       <c r="C173">
-        <v>0.4473684210526316</v>
+        <v>0.35789473684210527</v>
       </c>
       <c r="D173">
-        <v>0.6710526315789473</v>
+        <v>0.5368421052631579</v>
       </c>
     </row>
     <row r="174">
@@ -2445,13 +2445,13 @@
         <v>1.72</v>
       </c>
       <c r="B174">
-        <v>0.15566860465116278</v>
+        <v>0.12453488372093022</v>
       </c>
       <c r="C174">
-        <v>0.44476744186046513</v>
+        <v>0.3558139534883721</v>
       </c>
       <c r="D174">
-        <v>0.6671511627906976</v>
+        <v>0.5337209302325581</v>
       </c>
     </row>
     <row r="175">
@@ -2459,13 +2459,13 @@
         <v>1.73</v>
       </c>
       <c r="B175">
-        <v>0.15476878612716763</v>
+        <v>0.1238150289017341</v>
       </c>
       <c r="C175">
-        <v>0.44219653179190754</v>
+        <v>0.353757225433526</v>
       </c>
       <c r="D175">
-        <v>0.6632947976878614</v>
+        <v>0.530635838150289</v>
       </c>
     </row>
     <row r="176">
@@ -2473,13 +2473,13 @@
         <v>1.74</v>
       </c>
       <c r="B176">
-        <v>0.15387931034482757</v>
+        <v>0.12310344827586206</v>
       </c>
       <c r="C176">
-        <v>0.4396551724137931</v>
+        <v>0.35172413793103446</v>
       </c>
       <c r="D176">
-        <v>0.6594827586206896</v>
+        <v>0.5275862068965517</v>
       </c>
     </row>
     <row r="177">
@@ -2487,13 +2487,13 @@
         <v>1.75</v>
       </c>
       <c r="B177">
-        <v>0.153</v>
+        <v>0.12239999999999998</v>
       </c>
       <c r="C177">
-        <v>0.43714285714285717</v>
+        <v>0.3497142857142857</v>
       </c>
       <c r="D177">
-        <v>0.6557142857142857</v>
+        <v>0.5245714285714286</v>
       </c>
     </row>
     <row r="178">
@@ -2501,13 +2501,13 @@
         <v>1.76</v>
       </c>
       <c r="B178">
-        <v>0.15213068181818182</v>
+        <v>0.12170454545454544</v>
       </c>
       <c r="C178">
-        <v>0.43465909090909094</v>
+        <v>0.3477272727272727</v>
       </c>
       <c r="D178">
-        <v>0.6519886363636365</v>
+        <v>0.5215909090909091</v>
       </c>
     </row>
     <row r="179">
@@ -2515,13 +2515,13 @@
         <v>1.77</v>
       </c>
       <c r="B179">
-        <v>0.15127118644067797</v>
+        <v>0.12101694915254237</v>
       </c>
       <c r="C179">
-        <v>0.4322033898305085</v>
+        <v>0.34576271186440677</v>
       </c>
       <c r="D179">
-        <v>0.6483050847457628</v>
+        <v>0.5186440677966102</v>
       </c>
     </row>
     <row r="180">
@@ -2529,13 +2529,13 @@
         <v>1.78</v>
       </c>
       <c r="B180">
-        <v>0.15042134831460674</v>
+        <v>0.12033707865168539</v>
       </c>
       <c r="C180">
-        <v>0.4297752808988764</v>
+        <v>0.3438202247191011</v>
       </c>
       <c r="D180">
-        <v>0.6446629213483146</v>
+        <v>0.5157303370786517</v>
       </c>
     </row>
     <row r="181">
@@ -2543,13 +2543,13 @@
         <v>1.79</v>
       </c>
       <c r="B181">
-        <v>0.14958100558659218</v>
+        <v>0.11966480446927373</v>
       </c>
       <c r="C181">
-        <v>0.4273743016759777</v>
+        <v>0.3418994413407821</v>
       </c>
       <c r="D181">
-        <v>0.6410614525139665</v>
+        <v>0.5128491620111731</v>
       </c>
     </row>
     <row r="182">
@@ -2557,13 +2557,13 @@
         <v>1.8</v>
       </c>
       <c r="B182">
-        <v>0.14875</v>
+        <v>0.11899999999999998</v>
       </c>
       <c r="C182">
-        <v>0.425</v>
+        <v>0.33999999999999997</v>
       </c>
       <c r="D182">
-        <v>0.6375</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="183">
@@ -2571,13 +2571,13 @@
         <v>1.81</v>
       </c>
       <c r="B183">
-        <v>0.1479281767955801</v>
+        <v>0.11834254143646408</v>
       </c>
       <c r="C183">
-        <v>0.42265193370165743</v>
+        <v>0.33812154696132596</v>
       </c>
       <c r="D183">
-        <v>0.6339779005524862</v>
+        <v>0.507182320441989</v>
       </c>
     </row>
     <row r="184">
@@ -2585,13 +2585,13 @@
         <v>1.82</v>
       </c>
       <c r="B184">
-        <v>0.14711538461538462</v>
+        <v>0.11769230769230768</v>
       </c>
       <c r="C184">
-        <v>0.42032967032967034</v>
+        <v>0.33626373626373623</v>
       </c>
       <c r="D184">
-        <v>0.6304945054945055</v>
+        <v>0.5043956043956044</v>
       </c>
     </row>
     <row r="185">
@@ -2599,13 +2599,13 @@
         <v>1.83</v>
       </c>
       <c r="B185">
-        <v>0.14631147540983605</v>
+        <v>0.11704918032786885</v>
       </c>
       <c r="C185">
-        <v>0.41803278688524587</v>
+        <v>0.3344262295081967</v>
       </c>
       <c r="D185">
-        <v>0.6270491803278688</v>
+        <v>0.5016393442622951</v>
       </c>
     </row>
     <row r="186">
@@ -2613,13 +2613,13 @@
         <v>1.84</v>
       </c>
       <c r="B186">
-        <v>0.1455163043478261</v>
+        <v>0.11641304347826086</v>
       </c>
       <c r="C186">
-        <v>0.4157608695652174</v>
+        <v>0.3326086956521739</v>
       </c>
       <c r="D186">
-        <v>0.6236413043478262</v>
+        <v>0.4989130434782608</v>
       </c>
     </row>
     <row r="187">
@@ -2627,13 +2627,13 @@
         <v>1.85</v>
       </c>
       <c r="B187">
-        <v>0.14472972972972972</v>
+        <v>0.11578378378378376</v>
       </c>
       <c r="C187">
-        <v>0.4135135135135135</v>
+        <v>0.33081081081081076</v>
       </c>
       <c r="D187">
-        <v>0.6202702702702703</v>
+        <v>0.49621621621621614</v>
       </c>
     </row>
     <row r="188">
@@ -2641,13 +2641,13 @@
         <v>1.86</v>
       </c>
       <c r="B188">
-        <v>0.14395161290322578</v>
+        <v>0.11516129032258061</v>
       </c>
       <c r="C188">
-        <v>0.41129032258064513</v>
+        <v>0.3290322580645161</v>
       </c>
       <c r="D188">
-        <v>0.6169354838709677</v>
+        <v>0.4935483870967741</v>
       </c>
     </row>
     <row r="189">
@@ -2655,13 +2655,13 @@
         <v>1.87</v>
       </c>
       <c r="B189">
-        <v>0.14318181818181816</v>
+        <v>0.11454545454545453</v>
       </c>
       <c r="C189">
-        <v>0.40909090909090906</v>
+        <v>0.32727272727272727</v>
       </c>
       <c r="D189">
-        <v>0.6136363636363635</v>
+        <v>0.4909090909090909</v>
       </c>
     </row>
     <row r="190">
@@ -2669,13 +2669,13 @@
         <v>1.88</v>
       </c>
       <c r="B190">
-        <v>0.14242021276595745</v>
+        <v>0.11393617021276596</v>
       </c>
       <c r="C190">
-        <v>0.4069148936170213</v>
+        <v>0.32553191489361705</v>
       </c>
       <c r="D190">
-        <v>0.610372340425532</v>
+        <v>0.48829787234042554</v>
       </c>
     </row>
     <row r="191">
@@ -2683,13 +2683,13 @@
         <v>1.89</v>
       </c>
       <c r="B191">
-        <v>0.14166666666666666</v>
+        <v>0.11333333333333333</v>
       </c>
       <c r="C191">
-        <v>0.40476190476190477</v>
+        <v>0.3238095238095238</v>
       </c>
       <c r="D191">
-        <v>0.6071428571428572</v>
+        <v>0.48571428571428577</v>
       </c>
     </row>
     <row r="192">
@@ -2697,13 +2697,13 @@
         <v>1.9</v>
       </c>
       <c r="B192">
-        <v>0.14092105263157895</v>
+        <v>0.11273684210526315</v>
       </c>
       <c r="C192">
-        <v>0.40263157894736845</v>
+        <v>0.32210526315789473</v>
       </c>
       <c r="D192">
-        <v>0.6039473684210527</v>
+        <v>0.4831578947368421</v>
       </c>
     </row>
     <row r="193">
@@ -2711,13 +2711,13 @@
         <v>1.91</v>
       </c>
       <c r="B193">
-        <v>0.14018324607329843</v>
+        <v>0.11214659685863874</v>
       </c>
       <c r="C193">
-        <v>0.4005235602094241</v>
+        <v>0.3204188481675393</v>
       </c>
       <c r="D193">
-        <v>0.6007853403141361</v>
+        <v>0.48062827225130894</v>
       </c>
     </row>
     <row r="194">
@@ -2725,13 +2725,13 @@
         <v>1.92</v>
       </c>
       <c r="B194">
-        <v>0.13945312499999998</v>
+        <v>0.11156250000000001</v>
       </c>
       <c r="C194">
-        <v>0.3984375</v>
+        <v>0.31875000000000003</v>
       </c>
       <c r="D194">
-        <v>0.59765625</v>
+        <v>0.478125</v>
       </c>
     </row>
     <row r="195">
@@ -2739,13 +2739,13 @@
         <v>1.93</v>
       </c>
       <c r="B195">
-        <v>0.13873056994818653</v>
+        <v>0.11098445595854922</v>
       </c>
       <c r="C195">
-        <v>0.3963730569948187</v>
+        <v>0.3170984455958549</v>
       </c>
       <c r="D195">
-        <v>0.594559585492228</v>
+        <v>0.47564766839378236</v>
       </c>
     </row>
     <row r="196">
@@ -2753,13 +2753,13 @@
         <v>1.94</v>
       </c>
       <c r="B196">
-        <v>0.13801546391752578</v>
+        <v>0.11041237113402061</v>
       </c>
       <c r="C196">
-        <v>0.39432989690721654</v>
+        <v>0.3154639175257732</v>
       </c>
       <c r="D196">
-        <v>0.5914948453608249</v>
+        <v>0.4731958762886598</v>
       </c>
     </row>
     <row r="197">
@@ -2767,13 +2767,13 @@
         <v>1.95</v>
       </c>
       <c r="B197">
-        <v>0.1373076923076923</v>
+        <v>0.10984615384615383</v>
       </c>
       <c r="C197">
-        <v>0.3923076923076923</v>
+        <v>0.31384615384615383</v>
       </c>
       <c r="D197">
-        <v>0.5884615384615385</v>
+        <v>0.4707692307692307</v>
       </c>
     </row>
     <row r="198">
@@ -2781,13 +2781,13 @@
         <v>1.96</v>
       </c>
       <c r="B198">
-        <v>0.13660714285714284</v>
+        <v>0.10928571428571429</v>
       </c>
       <c r="C198">
-        <v>0.3903061224489796</v>
+        <v>0.3122448979591837</v>
       </c>
       <c r="D198">
-        <v>0.5854591836734694</v>
+        <v>0.4683673469387756</v>
       </c>
     </row>
     <row r="199">
@@ -2795,13 +2795,13 @@
         <v>1.97</v>
       </c>
       <c r="B199">
-        <v>0.13591370558375634</v>
+        <v>0.10873096446700507</v>
       </c>
       <c r="C199">
-        <v>0.3883248730964467</v>
+        <v>0.31065989847715736</v>
       </c>
       <c r="D199">
-        <v>0.5824873096446701</v>
+        <v>0.46598984771573604</v>
       </c>
     </row>
     <row r="200">
@@ -2809,13 +2809,13 @@
         <v>1.98</v>
       </c>
       <c r="B200">
-        <v>0.13522727272727272</v>
+        <v>0.10818181818181817</v>
       </c>
       <c r="C200">
-        <v>0.38636363636363635</v>
+        <v>0.3090909090909091</v>
       </c>
       <c r="D200">
-        <v>0.5795454545454546</v>
+        <v>0.4636363636363636</v>
       </c>
     </row>
     <row r="201">
@@ -2823,13 +2823,13 @@
         <v>1.99</v>
       </c>
       <c r="B201">
-        <v>0.13454773869346734</v>
+        <v>0.10763819095477387</v>
       </c>
       <c r="C201">
-        <v>0.3844221105527638</v>
+        <v>0.3075376884422111</v>
       </c>
       <c r="D201">
-        <v>0.5766331658291457</v>
+        <v>0.4613065326633166</v>
       </c>
     </row>
     <row r="202">
@@ -2837,13 +2837,13 @@
         <v>2.0</v>
       </c>
       <c r="B202">
-        <v>0.133875</v>
+        <v>0.10709999999999999</v>
       </c>
       <c r="C202">
-        <v>0.3825</v>
+        <v>0.306</v>
       </c>
       <c r="D202">
-        <v>0.57375</v>
+        <v>0.45899999999999996</v>
       </c>
     </row>
     <row r="203">
@@ -2851,13 +2851,13 @@
         <v>2.01</v>
       </c>
       <c r="B203">
-        <v>0.1332089552238806</v>
+        <v>0.10656716417910449</v>
       </c>
       <c r="C203">
-        <v>0.3805970149253732</v>
+        <v>0.30447761194029854</v>
       </c>
       <c r="D203">
-        <v>0.5708955223880597</v>
+        <v>0.4567164179104478</v>
       </c>
     </row>
     <row r="204">
@@ -2865,13 +2865,13 @@
         <v>2.02</v>
       </c>
       <c r="B204">
-        <v>0.13254950495049503</v>
+        <v>0.10603960396039604</v>
       </c>
       <c r="C204">
-        <v>0.3787128712871287</v>
+        <v>0.30297029702970296</v>
       </c>
       <c r="D204">
-        <v>0.568069306930693</v>
+        <v>0.4544554455445544</v>
       </c>
     </row>
     <row r="205">
@@ -2879,13 +2879,13 @@
         <v>2.03</v>
       </c>
       <c r="B205">
-        <v>0.13189655172413794</v>
+        <v>0.10551724137931034</v>
       </c>
       <c r="C205">
-        <v>0.37684729064039413</v>
+        <v>0.3014778325123153</v>
       </c>
       <c r="D205">
-        <v>0.5652709359605912</v>
+        <v>0.45221674876847295</v>
       </c>
     </row>
     <row r="206">
@@ -2893,13 +2893,13 @@
         <v>2.04</v>
       </c>
       <c r="B206">
-        <v>0.13124999999999998</v>
+        <v>0.105</v>
       </c>
       <c r="C206">
-        <v>0.375</v>
+        <v>0.3</v>
       </c>
       <c r="D206">
-        <v>0.5625</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="207">
@@ -2907,13 +2907,13 @@
         <v>2.05</v>
       </c>
       <c r="B207">
-        <v>0.13060975609756098</v>
+        <v>0.10448780487804879</v>
       </c>
       <c r="C207">
-        <v>0.3731707317073171</v>
+        <v>0.2985365853658537</v>
       </c>
       <c r="D207">
-        <v>0.5597560975609757</v>
+        <v>0.44780487804878055</v>
       </c>
     </row>
     <row r="208">
@@ -2921,13 +2921,13 @@
         <v>2.06</v>
       </c>
       <c r="B208">
-        <v>0.1299757281553398</v>
+        <v>0.10398058252427182</v>
       </c>
       <c r="C208">
-        <v>0.3713592233009709</v>
+        <v>0.29708737864077667</v>
       </c>
       <c r="D208">
-        <v>0.5570388349514563</v>
+        <v>0.44563106796116503</v>
       </c>
     </row>
     <row r="209">
@@ -2935,13 +2935,13 @@
         <v>2.07</v>
       </c>
       <c r="B209">
-        <v>0.12934782608695652</v>
+        <v>0.10347826086956521</v>
       </c>
       <c r="C209">
-        <v>0.3695652173913044</v>
+        <v>0.2956521739130435</v>
       </c>
       <c r="D209">
-        <v>0.5543478260869565</v>
+        <v>0.4434782608695652</v>
       </c>
     </row>
     <row r="210">
@@ -2949,13 +2949,13 @@
         <v>2.08</v>
       </c>
       <c r="B210">
-        <v>0.12872596153846153</v>
+        <v>0.10298076923076922</v>
       </c>
       <c r="C210">
-        <v>0.3677884615384615</v>
+        <v>0.29423076923076924</v>
       </c>
       <c r="D210">
-        <v>0.5516826923076923</v>
+        <v>0.44134615384615383</v>
       </c>
     </row>
     <row r="211">
@@ -2963,13 +2963,13 @@
         <v>2.09</v>
       </c>
       <c r="B211">
-        <v>0.12811004784688995</v>
+        <v>0.10248803827751196</v>
       </c>
       <c r="C211">
-        <v>0.3660287081339713</v>
+        <v>0.29282296650717704</v>
       </c>
       <c r="D211">
-        <v>0.549043062200957</v>
+        <v>0.43923444976076553</v>
       </c>
     </row>
     <row r="212">
@@ -2977,13 +2977,13 @@
         <v>2.1</v>
       </c>
       <c r="B212">
-        <v>0.12749999999999997</v>
+        <v>0.102</v>
       </c>
       <c r="C212">
-        <v>0.36428571428571427</v>
+        <v>0.2914285714285714</v>
       </c>
       <c r="D212">
-        <v>0.5464285714285714</v>
+        <v>0.43714285714285717</v>
       </c>
     </row>
     <row r="213">
@@ -2991,13 +2991,13 @@
         <v>2.11</v>
       </c>
       <c r="B213">
-        <v>0.1268957345971564</v>
+        <v>0.10151658767772512</v>
       </c>
       <c r="C213">
-        <v>0.36255924170616116</v>
+        <v>0.2900473933649289</v>
       </c>
       <c r="D213">
-        <v>0.5438388625592417</v>
+        <v>0.43507109004739336</v>
       </c>
     </row>
     <row r="214">
@@ -3005,13 +3005,13 @@
         <v>2.12</v>
       </c>
       <c r="B214">
-        <v>0.12629716981132075</v>
+        <v>0.10103773584905659</v>
       </c>
       <c r="C214">
-        <v>0.3608490566037736</v>
+        <v>0.28867924528301886</v>
       </c>
       <c r="D214">
-        <v>0.5412735849056604</v>
+        <v>0.43301886792452826</v>
       </c>
     </row>
     <row r="215">
@@ -3019,13 +3019,13 @@
         <v>2.13</v>
       </c>
       <c r="B215">
-        <v>0.12570422535211268</v>
+        <v>0.10056338028169014</v>
       </c>
       <c r="C215">
-        <v>0.3591549295774648</v>
+        <v>0.28732394366197184</v>
       </c>
       <c r="D215">
-        <v>0.5387323943661972</v>
+        <v>0.4309859154929577</v>
       </c>
     </row>
     <row r="216">
@@ -3033,13 +3033,13 @@
         <v>2.14</v>
       </c>
       <c r="B216">
-        <v>0.12511682242990654</v>
+        <v>0.10009345794392523</v>
       </c>
       <c r="C216">
-        <v>0.3574766355140187</v>
+        <v>0.28598130841121494</v>
       </c>
       <c r="D216">
-        <v>0.5362149532710281</v>
+        <v>0.4289719626168224</v>
       </c>
     </row>
     <row r="217">
@@ -3047,13 +3047,13 @@
         <v>2.15</v>
       </c>
       <c r="B217">
-        <v>0.12453488372093025</v>
+        <v>0.09962790697674419</v>
       </c>
       <c r="C217">
-        <v>0.35581395348837214</v>
+        <v>0.2846511627906977</v>
       </c>
       <c r="D217">
-        <v>0.5337209302325582</v>
+        <v>0.42697674418604653</v>
       </c>
     </row>
     <row r="218">
@@ -3061,13 +3061,13 @@
         <v>2.16</v>
       </c>
       <c r="B218">
-        <v>0.12395833333333331</v>
+        <v>0.09916666666666665</v>
       </c>
       <c r="C218">
-        <v>0.35416666666666663</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="D218">
-        <v>0.53125</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="219">
@@ -3075,13 +3075,13 @@
         <v>2.17</v>
       </c>
       <c r="B219">
-        <v>0.12338709677419354</v>
+        <v>0.09870967741935484</v>
       </c>
       <c r="C219">
-        <v>0.3525345622119816</v>
+        <v>0.2820276497695853</v>
       </c>
       <c r="D219">
-        <v>0.5288018433179724</v>
+        <v>0.4230414746543779</v>
       </c>
     </row>
     <row r="220">
@@ -3089,13 +3089,13 @@
         <v>2.18</v>
       </c>
       <c r="B220">
-        <v>0.12282110091743119</v>
+        <v>0.09825688073394494</v>
       </c>
       <c r="C220">
-        <v>0.35091743119266056</v>
+        <v>0.2807339449541284</v>
       </c>
       <c r="D220">
-        <v>0.5263761467889908</v>
+        <v>0.4211009174311926</v>
       </c>
     </row>
     <row r="221">
@@ -3103,13 +3103,13 @@
         <v>2.19</v>
       </c>
       <c r="B221">
-        <v>0.12226027397260274</v>
+        <v>0.09780821917808219</v>
       </c>
       <c r="C221">
-        <v>0.3493150684931507</v>
+        <v>0.27945205479452057</v>
       </c>
       <c r="D221">
-        <v>0.523972602739726</v>
+        <v>0.4191780821917809</v>
       </c>
     </row>
     <row r="222">
@@ -3117,13 +3117,13 @@
         <v>2.2</v>
       </c>
       <c r="B222">
-        <v>0.12170454545454544</v>
+        <v>0.09736363636363635</v>
       </c>
       <c r="C222">
-        <v>0.3477272727272727</v>
+        <v>0.27818181818181814</v>
       </c>
       <c r="D222">
-        <v>0.5215909090909091</v>
+        <v>0.41727272727272724</v>
       </c>
     </row>
     <row r="223">
@@ -3131,13 +3131,13 @@
         <v>2.21</v>
       </c>
       <c r="B223">
-        <v>0.12115384615384614</v>
+        <v>0.09692307692307692</v>
       </c>
       <c r="C223">
-        <v>0.34615384615384615</v>
+        <v>0.27692307692307694</v>
       </c>
       <c r="D223">
-        <v>0.5192307692307692</v>
+        <v>0.4153846153846154</v>
       </c>
     </row>
     <row r="224">
@@ -3145,13 +3145,13 @@
         <v>2.22</v>
       </c>
       <c r="B224">
-        <v>0.1206081081081081</v>
+        <v>0.09648648648648647</v>
       </c>
       <c r="C224">
-        <v>0.34459459459459457</v>
+        <v>0.27567567567567564</v>
       </c>
       <c r="D224">
-        <v>0.5168918918918919</v>
+        <v>0.41351351351351345</v>
       </c>
     </row>
     <row r="225">
@@ -3159,13 +3159,13 @@
         <v>2.23</v>
       </c>
       <c r="B225">
-        <v>0.12006726457399101</v>
+        <v>0.09605381165919281</v>
       </c>
       <c r="C225">
-        <v>0.3430493273542601</v>
+        <v>0.27443946188340806</v>
       </c>
       <c r="D225">
-        <v>0.5145739910313901</v>
+        <v>0.4116591928251121</v>
       </c>
     </row>
     <row r="226">
@@ -3173,13 +3173,13 @@
         <v>2.24</v>
       </c>
       <c r="B226">
-        <v>0.11953124999999998</v>
+        <v>0.09562499999999999</v>
       </c>
       <c r="C226">
-        <v>0.3415178571428571</v>
+        <v>0.2732142857142857</v>
       </c>
       <c r="D226">
-        <v>0.5122767857142856</v>
+        <v>0.40982142857142856</v>
       </c>
     </row>
     <row r="227">
@@ -3187,13 +3187,13 @@
         <v>2.25</v>
       </c>
       <c r="B227">
-        <v>0.119</v>
+        <v>0.0952</v>
       </c>
       <c r="C227">
-        <v>0.34</v>
+        <v>0.272</v>
       </c>
       <c r="D227">
-        <v>0.51</v>
+        <v>0.40800000000000003</v>
       </c>
     </row>
     <row r="228">
@@ -3201,13 +3201,13 @@
         <v>2.26</v>
       </c>
       <c r="B228">
-        <v>0.11847345132743363</v>
+        <v>0.0947787610619469</v>
       </c>
       <c r="C228">
-        <v>0.33849557522123896</v>
+        <v>0.27079646017699116</v>
       </c>
       <c r="D228">
-        <v>0.5077433628318584</v>
+        <v>0.4061946902654867</v>
       </c>
     </row>
     <row r="229">
@@ -3215,13 +3215,13 @@
         <v>2.27</v>
       </c>
       <c r="B229">
-        <v>0.11795154185022026</v>
+        <v>0.09436123348017621</v>
       </c>
       <c r="C229">
-        <v>0.3370044052863436</v>
+        <v>0.2696035242290749</v>
       </c>
       <c r="D229">
-        <v>0.5055066079295154</v>
+        <v>0.4044052863436124</v>
       </c>
     </row>
     <row r="230">
@@ -3229,13 +3229,13 @@
         <v>2.28</v>
       </c>
       <c r="B230">
-        <v>0.1174342105263158</v>
+        <v>0.09394736842105263</v>
       </c>
       <c r="C230">
-        <v>0.33552631578947373</v>
+        <v>0.26842105263157895</v>
       </c>
       <c r="D230">
-        <v>0.5032894736842106</v>
+        <v>0.40263157894736845</v>
       </c>
     </row>
     <row r="231">
@@ -3243,13 +3243,13 @@
         <v>2.29</v>
       </c>
       <c r="B231">
-        <v>0.11692139737991265</v>
+        <v>0.09353711790393011</v>
       </c>
       <c r="C231">
-        <v>0.33406113537117904</v>
+        <v>0.2672489082969432</v>
       </c>
       <c r="D231">
-        <v>0.5010917030567685</v>
+        <v>0.4008733624454148</v>
       </c>
     </row>
     <row r="232">
@@ -3257,13 +3257,13 @@
         <v>2.3</v>
       </c>
       <c r="B232">
-        <v>0.11641304347826087</v>
+        <v>0.0931304347826087</v>
       </c>
       <c r="C232">
-        <v>0.33260869565217394</v>
+        <v>0.26608695652173914</v>
       </c>
       <c r="D232">
-        <v>0.49891304347826093</v>
+        <v>0.3991304347826087</v>
       </c>
     </row>
     <row r="233">
@@ -3271,13 +3271,13 @@
         <v>2.31</v>
       </c>
       <c r="B233">
-        <v>0.1159090909090909</v>
+        <v>0.09272727272727271</v>
       </c>
       <c r="C233">
-        <v>0.33116883116883117</v>
+        <v>0.2649350649350649</v>
       </c>
       <c r="D233">
-        <v>0.4967532467532467</v>
+        <v>0.39740259740259737</v>
       </c>
     </row>
     <row r="234">
@@ -3285,13 +3285,13 @@
         <v>2.32</v>
       </c>
       <c r="B234">
-        <v>0.11540948275862069</v>
+        <v>0.09232758620689656</v>
       </c>
       <c r="C234">
-        <v>0.32974137931034486</v>
+        <v>0.2637931034482759</v>
       </c>
       <c r="D234">
-        <v>0.4946120689655173</v>
+        <v>0.39568965517241383</v>
       </c>
     </row>
     <row r="235">
@@ -3299,13 +3299,13 @@
         <v>2.33</v>
       </c>
       <c r="B235">
-        <v>0.11491416309012874</v>
+        <v>0.09193133047210299</v>
       </c>
       <c r="C235">
-        <v>0.3283261802575107</v>
+        <v>0.26266094420600855</v>
       </c>
       <c r="D235">
-        <v>0.49248927038626605</v>
+        <v>0.3939914163090128</v>
       </c>
     </row>
     <row r="236">
@@ -3313,13 +3313,13 @@
         <v>2.34</v>
       </c>
       <c r="B236">
-        <v>0.11442307692307692</v>
+        <v>0.09153846153846154</v>
       </c>
       <c r="C236">
-        <v>0.3269230769230769</v>
+        <v>0.26153846153846155</v>
       </c>
       <c r="D236">
-        <v>0.4903846153846154</v>
+        <v>0.39230769230769236</v>
       </c>
     </row>
     <row r="237">
@@ -3327,13 +3327,13 @@
         <v>2.35</v>
       </c>
       <c r="B237">
-        <v>0.11393617021276593</v>
+        <v>0.09114893617021275</v>
       </c>
       <c r="C237">
-        <v>0.325531914893617</v>
+        <v>0.2604255319148936</v>
       </c>
       <c r="D237">
-        <v>0.4882978723404255</v>
+        <v>0.3906382978723404</v>
       </c>
     </row>
     <row r="238">
@@ -3341,13 +3341,13 @@
         <v>2.36</v>
       </c>
       <c r="B238">
-        <v>0.11345338983050847</v>
+        <v>0.09076271186440678</v>
       </c>
       <c r="C238">
-        <v>0.3241525423728814</v>
+        <v>0.2593220338983051</v>
       </c>
       <c r="D238">
-        <v>0.48622881355932207</v>
+        <v>0.38898305084745766</v>
       </c>
     </row>
     <row r="239">
@@ -3355,13 +3355,13 @@
         <v>2.37</v>
       </c>
       <c r="B239">
-        <v>0.11297468354430379</v>
+        <v>0.09037974683544303</v>
       </c>
       <c r="C239">
-        <v>0.3227848101265823</v>
+        <v>0.2582278481012658</v>
       </c>
       <c r="D239">
-        <v>0.48417721518987344</v>
+        <v>0.3873417721518987</v>
       </c>
     </row>
     <row r="240">
@@ -3369,13 +3369,13 @@
         <v>2.38</v>
       </c>
       <c r="B240">
-        <v>0.1125</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="C240">
-        <v>0.32142857142857145</v>
+        <v>0.2571428571428572</v>
       </c>
       <c r="D240">
-        <v>0.4821428571428572</v>
+        <v>0.3857142857142858</v>
       </c>
     </row>
     <row r="241">
@@ -3383,13 +3383,13 @@
         <v>2.39</v>
       </c>
       <c r="B241">
-        <v>0.11202928870292886</v>
+        <v>0.08962343096234307</v>
       </c>
       <c r="C241">
-        <v>0.3200836820083682</v>
+        <v>0.2560669456066945</v>
       </c>
       <c r="D241">
-        <v>0.4801255230125523</v>
+        <v>0.3841004184100418</v>
       </c>
     </row>
     <row r="242">
@@ -3397,13 +3397,13 @@
         <v>2.4</v>
       </c>
       <c r="B242">
-        <v>0.11156250000000001</v>
+        <v>0.08925</v>
       </c>
       <c r="C242">
-        <v>0.31875000000000003</v>
+        <v>0.255</v>
       </c>
       <c r="D242">
-        <v>0.478125</v>
+        <v>0.3825</v>
       </c>
     </row>
     <row r="243">
@@ -3411,13 +3411,13 @@
         <v>2.41</v>
       </c>
       <c r="B243">
-        <v>0.11109958506224064</v>
+        <v>0.08887966804979253</v>
       </c>
       <c r="C243">
-        <v>0.31742738589211617</v>
+        <v>0.25394190871369293</v>
       </c>
       <c r="D243">
-        <v>0.47614107883817425</v>
+        <v>0.3809128630705394</v>
       </c>
     </row>
     <row r="244">
@@ -3425,13 +3425,13 @@
         <v>2.42</v>
       </c>
       <c r="B244">
-        <v>0.11064049586776858</v>
+        <v>0.08851239669421487</v>
       </c>
       <c r="C244">
-        <v>0.31611570247933884</v>
+        <v>0.2528925619834711</v>
       </c>
       <c r="D244">
-        <v>0.47417355371900827</v>
+        <v>0.37933884297520665</v>
       </c>
     </row>
     <row r="245">
@@ -3439,13 +3439,13 @@
         <v>2.43</v>
       </c>
       <c r="B245">
-        <v>0.11018518518518518</v>
+        <v>0.08814814814814813</v>
       </c>
       <c r="C245">
-        <v>0.3148148148148148</v>
+        <v>0.2518518518518518</v>
       </c>
       <c r="D245">
-        <v>0.4722222222222222</v>
+        <v>0.37777777777777777</v>
       </c>
     </row>
     <row r="246">
@@ -3453,13 +3453,13 @@
         <v>2.44</v>
       </c>
       <c r="B246">
-        <v>0.10973360655737703</v>
+        <v>0.08778688524590163</v>
       </c>
       <c r="C246">
-        <v>0.3135245901639344</v>
+        <v>0.25081967213114753</v>
       </c>
       <c r="D246">
-        <v>0.4702868852459016</v>
+        <v>0.3762295081967213</v>
       </c>
     </row>
     <row r="247">
@@ -3467,13 +3467,13 @@
         <v>2.45</v>
       </c>
       <c r="B247">
-        <v>0.10928571428571426</v>
+        <v>0.08742857142857141</v>
       </c>
       <c r="C247">
-        <v>0.31224489795918364</v>
+        <v>0.2497959183673469</v>
       </c>
       <c r="D247">
-        <v>0.46836734693877546</v>
+        <v>0.37469387755102035</v>
       </c>
     </row>
     <row r="248">
@@ -3481,13 +3481,13 @@
         <v>2.46</v>
       </c>
       <c r="B248">
-        <v>0.10884146341463415</v>
+        <v>0.08707317073170731</v>
       </c>
       <c r="C248">
-        <v>0.31097560975609756</v>
+        <v>0.24878048780487805</v>
       </c>
       <c r="D248">
-        <v>0.4664634146341463</v>
+        <v>0.37317073170731707</v>
       </c>
     </row>
     <row r="249">
@@ -3495,13 +3495,13 @@
         <v>2.47</v>
       </c>
       <c r="B249">
-        <v>0.10840080971659918</v>
+        <v>0.08672064777327934</v>
       </c>
       <c r="C249">
-        <v>0.3097165991902834</v>
+        <v>0.2477732793522267</v>
       </c>
       <c r="D249">
-        <v>0.46457489878542507</v>
+        <v>0.37165991902834006</v>
       </c>
     </row>
     <row r="250">
@@ -3509,13 +3509,13 @@
         <v>2.48</v>
       </c>
       <c r="B250">
-        <v>0.10796370967741935</v>
+        <v>0.08637096774193548</v>
       </c>
       <c r="C250">
-        <v>0.3084677419354839</v>
+        <v>0.2467741935483871</v>
       </c>
       <c r="D250">
-        <v>0.4627016129032258</v>
+        <v>0.3701612903225806</v>
       </c>
     </row>
     <row r="251">
@@ -3523,13 +3523,13 @@
         <v>2.49</v>
       </c>
       <c r="B251">
-        <v>0.1075301204819277</v>
+        <v>0.08602409638554216</v>
       </c>
       <c r="C251">
-        <v>0.3072289156626506</v>
+        <v>0.24578313253012046</v>
       </c>
       <c r="D251">
-        <v>0.46084337349397586</v>
+        <v>0.36867469879518067</v>
       </c>
     </row>
     <row r="252">
@@ -3537,13 +3537,13 @@
         <v>2.5</v>
       </c>
       <c r="B252">
-        <v>0.10709999999999999</v>
+        <v>0.08567999999999999</v>
       </c>
       <c r="C252">
-        <v>0.306</v>
+        <v>0.2448</v>
       </c>
       <c r="D252">
-        <v>0.45899999999999996</v>
+        <v>0.36719999999999997</v>
       </c>
     </row>
     <row r="253">
@@ -3551,13 +3551,13 @@
         <v>2.51</v>
       </c>
       <c r="B253">
-        <v>0.10667330677290836</v>
+        <v>0.0853386454183267</v>
       </c>
       <c r="C253">
-        <v>0.3047808764940239</v>
+        <v>0.24382470119521915</v>
       </c>
       <c r="D253">
-        <v>0.4571713147410359</v>
+        <v>0.3657370517928287</v>
       </c>
     </row>
     <row r="254">
@@ -3565,13 +3565,13 @@
         <v>2.52</v>
       </c>
       <c r="B254">
-        <v>0.10624999999999998</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="C254">
-        <v>0.30357142857142855</v>
+        <v>0.24285714285714285</v>
       </c>
       <c r="D254">
-        <v>0.4553571428571428</v>
+        <v>0.36428571428571427</v>
       </c>
     </row>
     <row r="255">
@@ -3579,13 +3579,13 @@
         <v>2.53</v>
       </c>
       <c r="B255">
-        <v>0.1058300395256917</v>
+        <v>0.08466403162055336</v>
       </c>
       <c r="C255">
-        <v>0.3023715415019763</v>
+        <v>0.24189723320158105</v>
       </c>
       <c r="D255">
-        <v>0.4535573122529645</v>
+        <v>0.36284584980237156</v>
       </c>
     </row>
     <row r="256">
@@ -3593,13 +3593,13 @@
         <v>2.54</v>
       </c>
       <c r="B256">
-        <v>0.10541338582677165</v>
+        <v>0.08433070866141731</v>
       </c>
       <c r="C256">
-        <v>0.30118110236220474</v>
+        <v>0.24094488188976376</v>
       </c>
       <c r="D256">
-        <v>0.4517716535433071</v>
+        <v>0.36141732283464567</v>
       </c>
     </row>
     <row r="257">
@@ -3607,13 +3607,13 @@
         <v>2.55</v>
       </c>
       <c r="B257">
-        <v>0.10500000000000001</v>
+        <v>0.084</v>
       </c>
       <c r="C257">
-        <v>0.30000000000000004</v>
+        <v>0.24000000000000002</v>
       </c>
       <c r="D257">
-        <v>0.45000000000000007</v>
+        <v>0.36000000000000004</v>
       </c>
     </row>
     <row r="258">
@@ -3621,13 +3621,13 @@
         <v>2.56</v>
       </c>
       <c r="B258">
-        <v>0.10458984375</v>
+        <v>0.08367187499999999</v>
       </c>
       <c r="C258">
-        <v>0.298828125</v>
+        <v>0.23906249999999998</v>
       </c>
       <c r="D258">
-        <v>0.4482421875</v>
+        <v>0.35859375</v>
       </c>
     </row>
     <row r="259">
@@ -3635,13 +3635,13 @@
         <v>2.57</v>
       </c>
       <c r="B259">
-        <v>0.1041828793774319</v>
+        <v>0.08334630350194552</v>
       </c>
       <c r="C259">
-        <v>0.29766536964980544</v>
+        <v>0.23813229571984437</v>
       </c>
       <c r="D259">
-        <v>0.44649805447470814</v>
+        <v>0.35719844357976654</v>
       </c>
     </row>
     <row r="260">
@@ -3649,13 +3649,13 @@
         <v>2.58</v>
       </c>
       <c r="B260">
-        <v>0.10377906976744185</v>
+        <v>0.08302325581395348</v>
       </c>
       <c r="C260">
-        <v>0.2965116279069767</v>
+        <v>0.23720930232558138</v>
       </c>
       <c r="D260">
-        <v>0.4447674418604651</v>
+        <v>0.3558139534883721</v>
       </c>
     </row>
     <row r="261">
@@ -3663,13 +3663,13 @@
         <v>2.59</v>
       </c>
       <c r="B261">
-        <v>0.10337837837837838</v>
+        <v>0.0827027027027027</v>
       </c>
       <c r="C261">
-        <v>0.2953667953667954</v>
+        <v>0.2362934362934363</v>
       </c>
       <c r="D261">
-        <v>0.4430501930501931</v>
+        <v>0.3544401544401544</v>
       </c>
     </row>
     <row r="262">
@@ -3677,13 +3677,13 @@
         <v>2.6</v>
       </c>
       <c r="B262">
-        <v>0.10298076923076922</v>
+        <v>0.08238461538461538</v>
       </c>
       <c r="C262">
-        <v>0.29423076923076924</v>
+        <v>0.23538461538461536</v>
       </c>
       <c r="D262">
-        <v>0.44134615384615383</v>
+        <v>0.35307692307692307</v>
       </c>
     </row>
     <row r="263">
@@ -3691,13 +3691,13 @@
         <v>2.61</v>
       </c>
       <c r="B263">
-        <v>0.10258620689655173</v>
+        <v>0.08206896551724137</v>
       </c>
       <c r="C263">
-        <v>0.2931034482758621</v>
+        <v>0.23448275862068965</v>
       </c>
       <c r="D263">
-        <v>0.43965517241379315</v>
+        <v>0.35172413793103446</v>
       </c>
     </row>
     <row r="264">
@@ -3705,13 +3705,13 @@
         <v>2.62</v>
       </c>
       <c r="B264">
-        <v>0.10219465648854961</v>
+        <v>0.08175572519083968</v>
       </c>
       <c r="C264">
-        <v>0.2919847328244275</v>
+        <v>0.23358778625954196</v>
       </c>
       <c r="D264">
-        <v>0.43797709923664124</v>
+        <v>0.35038167938931297</v>
       </c>
     </row>
     <row r="265">
@@ -3719,13 +3719,13 @@
         <v>2.63</v>
       </c>
       <c r="B265">
-        <v>0.10180608365019013</v>
+        <v>0.08144486692015208</v>
       </c>
       <c r="C265">
-        <v>0.29087452471482894</v>
+        <v>0.23269961977186313</v>
       </c>
       <c r="D265">
-        <v>0.4363117870722434</v>
+        <v>0.3490494296577947</v>
       </c>
     </row>
     <row r="266">
@@ -3733,13 +3733,13 @@
         <v>2.64</v>
       </c>
       <c r="B266">
-        <v>0.10142045454545452</v>
+        <v>0.08113636363636363</v>
       </c>
       <c r="C266">
-        <v>0.28977272727272724</v>
+        <v>0.2318181818181818</v>
       </c>
       <c r="D266">
-        <v>0.43465909090909083</v>
+        <v>0.3477272727272727</v>
       </c>
     </row>
     <row r="267">
@@ -3747,13 +3747,13 @@
         <v>2.65</v>
       </c>
       <c r="B267">
-        <v>0.10103773584905659</v>
+        <v>0.08083018867924528</v>
       </c>
       <c r="C267">
-        <v>0.28867924528301886</v>
+        <v>0.2309433962264151</v>
       </c>
       <c r="D267">
-        <v>0.43301886792452826</v>
+        <v>0.34641509433962264</v>
       </c>
     </row>
     <row r="268">
@@ -3761,13 +3761,13 @@
         <v>2.66</v>
       </c>
       <c r="B268">
-        <v>0.1006578947368421</v>
+        <v>0.08052631578947367</v>
       </c>
       <c r="C268">
-        <v>0.287593984962406</v>
+        <v>0.2300751879699248</v>
       </c>
       <c r="D268">
-        <v>0.431390977443609</v>
+        <v>0.3451127819548872</v>
       </c>
     </row>
     <row r="269">
@@ -3775,13 +3775,13 @@
         <v>2.67</v>
       </c>
       <c r="B269">
-        <v>0.1002808988764045</v>
+        <v>0.08022471910112358</v>
       </c>
       <c r="C269">
-        <v>0.2865168539325843</v>
+        <v>0.2292134831460674</v>
       </c>
       <c r="D269">
-        <v>0.42977528089887646</v>
+        <v>0.3438202247191011</v>
       </c>
     </row>
     <row r="270">
@@ -3789,13 +3789,13 @@
         <v>2.68</v>
       </c>
       <c r="B270">
-        <v>0.09990671641791044</v>
+        <v>0.07992537313432835</v>
       </c>
       <c r="C270">
-        <v>0.2854477611940298</v>
+        <v>0.22835820895522385</v>
       </c>
       <c r="D270">
-        <v>0.4281716417910447</v>
+        <v>0.3425373134328358</v>
       </c>
     </row>
     <row r="271">
@@ -3803,13 +3803,13 @@
         <v>2.69</v>
       </c>
       <c r="B271">
-        <v>0.09953531598513012</v>
+        <v>0.07962825278810409</v>
       </c>
       <c r="C271">
-        <v>0.2843866171003718</v>
+        <v>0.2275092936802974</v>
       </c>
       <c r="D271">
-        <v>0.4265799256505577</v>
+        <v>0.3412639405204461</v>
       </c>
     </row>
     <row r="272">
@@ -3817,13 +3817,13 @@
         <v>2.7</v>
       </c>
       <c r="B272">
-        <v>0.09916666666666665</v>
+        <v>0.07933333333333333</v>
       </c>
       <c r="C272">
-        <v>0.2833333333333333</v>
+        <v>0.22666666666666666</v>
       </c>
       <c r="D272">
-        <v>0.425</v>
+        <v>0.33999999999999997</v>
       </c>
     </row>
     <row r="273">
@@ -3831,13 +3831,13 @@
         <v>2.71</v>
       </c>
       <c r="B273">
-        <v>0.09880073800738007</v>
+        <v>0.07904059040590405</v>
       </c>
       <c r="C273">
-        <v>0.2822878228782288</v>
+        <v>0.22583025830258302</v>
       </c>
       <c r="D273">
-        <v>0.42343173431734316</v>
+        <v>0.3387453874538745</v>
       </c>
     </row>
     <row r="274">
@@ -3845,13 +3845,13 @@
         <v>2.72</v>
       </c>
       <c r="B274">
-        <v>0.0984375</v>
+        <v>0.07874999999999999</v>
       </c>
       <c r="C274">
-        <v>0.28125</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="D274">
-        <v>0.421875</v>
+        <v>0.33749999999999997</v>
       </c>
     </row>
     <row r="275">
@@ -3859,13 +3859,13 @@
         <v>2.73</v>
       </c>
       <c r="B275">
-        <v>0.09807692307692308</v>
+        <v>0.07846153846153846</v>
       </c>
       <c r="C275">
-        <v>0.2802197802197802</v>
+        <v>0.22417582417582418</v>
       </c>
       <c r="D275">
-        <v>0.42032967032967034</v>
+        <v>0.3362637362637363</v>
       </c>
     </row>
     <row r="276">
@@ -3873,13 +3873,13 @@
         <v>2.74</v>
       </c>
       <c r="B276">
-        <v>0.09771897810218977</v>
+        <v>0.07817518248175181</v>
       </c>
       <c r="C276">
-        <v>0.27919708029197077</v>
+        <v>0.2233576642335766</v>
       </c>
       <c r="D276">
-        <v>0.41879562043795615</v>
+        <v>0.3350364963503649</v>
       </c>
     </row>
     <row r="277">
@@ -3887,13 +3887,13 @@
         <v>2.75</v>
       </c>
       <c r="B277">
-        <v>0.09736363636363636</v>
+        <v>0.07789090909090908</v>
       </c>
       <c r="C277">
-        <v>0.2781818181818182</v>
+        <v>0.22254545454545455</v>
       </c>
       <c r="D277">
-        <v>0.4172727272727273</v>
+        <v>0.3338181818181818</v>
       </c>
     </row>
     <row r="278">
@@ -3901,13 +3901,13 @@
         <v>2.76</v>
       </c>
       <c r="B278">
-        <v>0.09701086956521739</v>
+        <v>0.07760869565217392</v>
       </c>
       <c r="C278">
-        <v>0.27717391304347827</v>
+        <v>0.22173913043478263</v>
       </c>
       <c r="D278">
-        <v>0.4157608695652174</v>
+        <v>0.33260869565217394</v>
       </c>
     </row>
     <row r="279">
@@ -3915,13 +3915,13 @@
         <v>2.77</v>
       </c>
       <c r="B279">
-        <v>0.09666064981949457</v>
+        <v>0.07732851985559566</v>
       </c>
       <c r="C279">
-        <v>0.27617328519855594</v>
+        <v>0.22093862815884477</v>
       </c>
       <c r="D279">
-        <v>0.41425992779783394</v>
+        <v>0.33140794223826714</v>
       </c>
     </row>
     <row r="280">
@@ -3929,13 +3929,13 @@
         <v>2.78</v>
       </c>
       <c r="B280">
-        <v>0.09631294964028776</v>
+        <v>0.07705035971223022</v>
       </c>
       <c r="C280">
-        <v>0.2751798561151079</v>
+        <v>0.22014388489208633</v>
       </c>
       <c r="D280">
-        <v>0.41276978417266186</v>
+        <v>0.3302158273381295</v>
       </c>
     </row>
     <row r="281">
@@ -3943,13 +3943,13 @@
         <v>2.79</v>
       </c>
       <c r="B281">
-        <v>0.09596774193548385</v>
+        <v>0.07677419354838709</v>
       </c>
       <c r="C281">
-        <v>0.27419354838709675</v>
+        <v>0.21935483870967742</v>
       </c>
       <c r="D281">
-        <v>0.41129032258064513</v>
+        <v>0.32903225806451614</v>
       </c>
     </row>
     <row r="282">
@@ -3957,13 +3957,13 @@
         <v>2.8</v>
       </c>
       <c r="B282">
-        <v>0.095625</v>
+        <v>0.0765</v>
       </c>
       <c r="C282">
-        <v>0.27321428571428574</v>
+        <v>0.21857142857142858</v>
       </c>
       <c r="D282">
-        <v>0.4098214285714286</v>
+        <v>0.32785714285714285</v>
       </c>
     </row>
     <row r="283">
@@ -3971,13 +3971,13 @@
         <v>2.81</v>
       </c>
       <c r="B283">
-        <v>0.0952846975088968</v>
+        <v>0.07622775800711742</v>
       </c>
       <c r="C283">
-        <v>0.2722419928825623</v>
+        <v>0.2177935943060498</v>
       </c>
       <c r="D283">
-        <v>0.4083629893238434</v>
+        <v>0.3266903914590747</v>
       </c>
     </row>
     <row r="284">
@@ -3985,13 +3985,13 @@
         <v>2.82</v>
       </c>
       <c r="B284">
-        <v>0.0949468085106383</v>
+        <v>0.07595744680851063</v>
       </c>
       <c r="C284">
-        <v>0.2712765957446809</v>
+        <v>0.2170212765957447</v>
       </c>
       <c r="D284">
-        <v>0.4069148936170213</v>
+        <v>0.32553191489361705</v>
       </c>
     </row>
     <row r="285">
@@ -3999,13 +3999,13 @@
         <v>2.83</v>
       </c>
       <c r="B285">
-        <v>0.09461130742049469</v>
+        <v>0.07568904593639575</v>
       </c>
       <c r="C285">
-        <v>0.2703180212014134</v>
+        <v>0.21625441696113074</v>
       </c>
       <c r="D285">
-        <v>0.40547703180212014</v>
+        <v>0.32438162544169613</v>
       </c>
     </row>
     <row r="286">
@@ -4013,13 +4013,13 @@
         <v>2.84</v>
       </c>
       <c r="B286">
-        <v>0.0942781690140845</v>
+        <v>0.07542253521126761</v>
       </c>
       <c r="C286">
-        <v>0.2693661971830986</v>
+        <v>0.2154929577464789</v>
       </c>
       <c r="D286">
-        <v>0.40404929577464793</v>
+        <v>0.3232394366197183</v>
       </c>
     </row>
     <row r="287">
@@ -4027,13 +4027,13 @@
         <v>2.85</v>
       </c>
       <c r="B287">
-        <v>0.09394736842105263</v>
+        <v>0.07515789473684209</v>
       </c>
       <c r="C287">
-        <v>0.26842105263157895</v>
+        <v>0.21473684210526314</v>
       </c>
       <c r="D287">
-        <v>0.40263157894736845</v>
+        <v>0.32210526315789473</v>
       </c>
     </row>
     <row r="288">
@@ -4041,13 +4041,13 @@
         <v>2.86</v>
       </c>
       <c r="B288">
-        <v>0.09361888111888111</v>
+        <v>0.0748951048951049</v>
       </c>
       <c r="C288">
-        <v>0.2674825174825175</v>
+        <v>0.213986013986014</v>
       </c>
       <c r="D288">
-        <v>0.40122377622377625</v>
+        <v>0.320979020979021</v>
       </c>
     </row>
     <row r="289">
@@ -4055,13 +4055,13 @@
         <v>2.87</v>
       </c>
       <c r="B289">
-        <v>0.09329268292682925</v>
+        <v>0.07463414634146341</v>
       </c>
       <c r="C289">
-        <v>0.2665505226480836</v>
+        <v>0.2132404181184669</v>
       </c>
       <c r="D289">
-        <v>0.3998257839721254</v>
+        <v>0.31986062717770036</v>
       </c>
     </row>
     <row r="290">
@@ -4069,13 +4069,13 @@
         <v>2.88</v>
       </c>
       <c r="B290">
-        <v>0.09296874999999999</v>
+        <v>0.074375</v>
       </c>
       <c r="C290">
-        <v>0.265625</v>
+        <v>0.2125</v>
       </c>
       <c r="D290">
-        <v>0.3984375</v>
+        <v>0.31875</v>
       </c>
     </row>
     <row r="291">
@@ -4083,13 +4083,13 @@
         <v>2.89</v>
       </c>
       <c r="B291">
-        <v>0.0926470588235294</v>
+        <v>0.07411764705882352</v>
       </c>
       <c r="C291">
-        <v>0.2647058823529412</v>
+        <v>0.21176470588235294</v>
       </c>
       <c r="D291">
-        <v>0.3970588235294118</v>
+        <v>0.3176470588235294</v>
       </c>
     </row>
     <row r="292">
@@ -4097,13 +4097,13 @@
         <v>2.9</v>
       </c>
       <c r="B292">
-        <v>0.09232758620689656</v>
+        <v>0.07386206896551724</v>
       </c>
       <c r="C292">
-        <v>0.2637931034482759</v>
+        <v>0.2110344827586207</v>
       </c>
       <c r="D292">
-        <v>0.39568965517241383</v>
+        <v>0.31655172413793103</v>
       </c>
     </row>
     <row r="293">
@@ -4111,13 +4111,13 @@
         <v>2.91</v>
       </c>
       <c r="B293">
-        <v>0.09201030927835051</v>
+        <v>0.07360824742268039</v>
       </c>
       <c r="C293">
-        <v>0.26288659793814434</v>
+        <v>0.21030927835051544</v>
       </c>
       <c r="D293">
-        <v>0.39432989690721654</v>
+        <v>0.3154639175257732</v>
       </c>
     </row>
     <row r="294">
@@ -4125,13 +4125,13 @@
         <v>2.92</v>
       </c>
       <c r="B294">
-        <v>0.09169520547945205</v>
+        <v>0.07335616438356164</v>
       </c>
       <c r="C294">
-        <v>0.261986301369863</v>
+        <v>0.2095890410958904</v>
       </c>
       <c r="D294">
-        <v>0.3929794520547945</v>
+        <v>0.31438356164383563</v>
       </c>
     </row>
     <row r="295">
@@ -4139,13 +4139,13 @@
         <v>2.93</v>
       </c>
       <c r="B295">
-        <v>0.09138225255972696</v>
+        <v>0.07310580204778155</v>
       </c>
       <c r="C295">
-        <v>0.26109215017064846</v>
+        <v>0.20887372013651875</v>
       </c>
       <c r="D295">
-        <v>0.3916382252559727</v>
+        <v>0.31331058020477814</v>
       </c>
     </row>
     <row r="296">
@@ -4153,13 +4153,13 @@
         <v>2.94</v>
       </c>
       <c r="B296">
-        <v>0.09107142857142857</v>
+        <v>0.07285714285714286</v>
       </c>
       <c r="C296">
-        <v>0.2602040816326531</v>
+        <v>0.20816326530612245</v>
       </c>
       <c r="D296">
-        <v>0.3903061224489796</v>
+        <v>0.31224489795918364</v>
       </c>
     </row>
     <row r="297">
@@ -4167,13 +4167,13 @@
         <v>2.95</v>
       </c>
       <c r="B297">
-        <v>0.09076271186440676</v>
+        <v>0.0726101694915254</v>
       </c>
       <c r="C297">
-        <v>0.25932203389830505</v>
+        <v>0.20745762711864404</v>
       </c>
       <c r="D297">
-        <v>0.38898305084745755</v>
+        <v>0.3111864406779661</v>
       </c>
     </row>
     <row r="298">
@@ -4181,13 +4181,13 @@
         <v>2.96</v>
       </c>
       <c r="B298">
-        <v>0.09045608108108108</v>
+        <v>0.07236486486486486</v>
       </c>
       <c r="C298">
-        <v>0.25844594594594594</v>
+        <v>0.20675675675675675</v>
       </c>
       <c r="D298">
-        <v>0.3876689189189189</v>
+        <v>0.31013513513513513</v>
       </c>
     </row>
     <row r="299">
@@ -4195,13 +4195,13 @@
         <v>2.97</v>
       </c>
       <c r="B299">
-        <v>0.09015151515151515</v>
+        <v>0.07212121212121211</v>
       </c>
       <c r="C299">
-        <v>0.25757575757575757</v>
+        <v>0.20606060606060606</v>
       </c>
       <c r="D299">
-        <v>0.38636363636363635</v>
+        <v>0.3090909090909091</v>
       </c>
     </row>
     <row r="300">
@@ -4209,13 +4209,13 @@
         <v>2.98</v>
       </c>
       <c r="B300">
-        <v>0.0898489932885906</v>
+        <v>0.07187919463087247</v>
       </c>
       <c r="C300">
-        <v>0.25671140939597314</v>
+        <v>0.20536912751677852</v>
       </c>
       <c r="D300">
-        <v>0.3850671140939597</v>
+        <v>0.3080536912751678</v>
       </c>
     </row>
     <row r="301">
@@ -4223,13 +4223,13 @@
         <v>2.99</v>
       </c>
       <c r="B301">
-        <v>0.08954849498327759</v>
+        <v>0.07163879598662205</v>
       </c>
       <c r="C301">
-        <v>0.25585284280936454</v>
+        <v>0.2046822742474916</v>
       </c>
       <c r="D301">
-        <v>0.38377926421404684</v>
+        <v>0.3070234113712374</v>
       </c>
     </row>
     <row r="302">
@@ -4237,13 +4237,13 @@
         <v>3.0</v>
       </c>
       <c r="B302">
-        <v>0.08925</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="C302">
-        <v>0.255</v>
+        <v>0.204</v>
       </c>
       <c r="D302">
-        <v>0.3825</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="303">
@@ -4251,13 +4251,13 @@
         <v>3.01</v>
       </c>
       <c r="B303">
-        <v>0.08895348837209302</v>
+        <v>0.07116279069767442</v>
       </c>
       <c r="C303">
-        <v>0.2541528239202658</v>
+        <v>0.20332225913621263</v>
       </c>
       <c r="D303">
-        <v>0.3812292358803987</v>
+        <v>0.30498338870431896</v>
       </c>
     </row>
     <row r="304">
@@ -4265,13 +4265,13 @@
         <v>3.02</v>
       </c>
       <c r="B304">
-        <v>0.08865894039735099</v>
+        <v>0.07092715231788078</v>
       </c>
       <c r="C304">
-        <v>0.2533112582781457</v>
+        <v>0.20264900662251656</v>
       </c>
       <c r="D304">
-        <v>0.37996688741721857</v>
+        <v>0.3039735099337748</v>
       </c>
     </row>
     <row r="305">
@@ -4279,13 +4279,13 @@
         <v>3.03</v>
       </c>
       <c r="B305">
-        <v>0.08836633663366336</v>
+        <v>0.07069306930693069</v>
       </c>
       <c r="C305">
-        <v>0.2524752475247525</v>
+        <v>0.201980198019802</v>
       </c>
       <c r="D305">
-        <v>0.3787128712871287</v>
+        <v>0.302970297029703</v>
       </c>
     </row>
     <row r="306">
@@ -4293,13 +4293,13 @@
         <v>3.04</v>
       </c>
       <c r="B306">
-        <v>0.08807565789473683</v>
+        <v>0.07046052631578946</v>
       </c>
       <c r="C306">
-        <v>0.25164473684210525</v>
+        <v>0.2013157894736842</v>
       </c>
       <c r="D306">
-        <v>0.37746710526315785</v>
+        <v>0.3019736842105263</v>
       </c>
     </row>
     <row r="307">
@@ -4307,13 +4307,13 @@
         <v>3.05</v>
       </c>
       <c r="B307">
-        <v>0.08778688524590166</v>
+        <v>0.07022950819672132</v>
       </c>
       <c r="C307">
-        <v>0.2508196721311476</v>
+        <v>0.20065573770491804</v>
       </c>
       <c r="D307">
-        <v>0.3762295081967214</v>
+        <v>0.30098360655737705</v>
       </c>
     </row>
     <row r="308">
@@ -4321,13 +4321,13 @@
         <v>3.06</v>
       </c>
       <c r="B308">
-        <v>0.0875</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="C308">
-        <v>0.25</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="D308">
-        <v>0.375</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="309">
@@ -4335,13 +4335,13 @@
         <v>3.07</v>
       </c>
       <c r="B309">
-        <v>0.08721498371335505</v>
+        <v>0.06977198697068403</v>
       </c>
       <c r="C309">
-        <v>0.24918566775244302</v>
+        <v>0.1993485342019544</v>
       </c>
       <c r="D309">
-        <v>0.37377850162866455</v>
+        <v>0.2990228013029316</v>
       </c>
     </row>
     <row r="310">
@@ -4349,13 +4349,13 @@
         <v>3.08</v>
       </c>
       <c r="B310">
-        <v>0.08693181818181817</v>
+        <v>0.06954545454545454</v>
       </c>
       <c r="C310">
-        <v>0.24837662337662336</v>
+        <v>0.19870129870129868</v>
       </c>
       <c r="D310">
-        <v>0.37256493506493504</v>
+        <v>0.298051948051948</v>
       </c>
     </row>
     <row r="311">
@@ -4363,13 +4363,13 @@
         <v>3.09</v>
       </c>
       <c r="B311">
-        <v>0.08665048543689322</v>
+        <v>0.06932038834951457</v>
       </c>
       <c r="C311">
-        <v>0.2475728155339806</v>
+        <v>0.19805825242718447</v>
       </c>
       <c r="D311">
-        <v>0.37135922330097093</v>
+        <v>0.2970873786407767</v>
       </c>
     </row>
     <row r="312">
@@ -4377,13 +4377,13 @@
         <v>3.1</v>
       </c>
       <c r="B312">
-        <v>0.08637096774193548</v>
+        <v>0.06909677419354839</v>
       </c>
       <c r="C312">
-        <v>0.2467741935483871</v>
+        <v>0.19741935483870968</v>
       </c>
       <c r="D312">
-        <v>0.3701612903225806</v>
+        <v>0.29612903225806453</v>
       </c>
     </row>
     <row r="313">
@@ -4391,13 +4391,13 @@
         <v>3.11</v>
       </c>
       <c r="B313">
-        <v>0.08609324758842443</v>
+        <v>0.06887459807073955</v>
       </c>
       <c r="C313">
-        <v>0.2459807073954984</v>
+        <v>0.19678456591639873</v>
       </c>
       <c r="D313">
-        <v>0.3689710610932476</v>
+        <v>0.2951768488745981</v>
       </c>
     </row>
     <row r="314">
@@ -4405,13 +4405,13 @@
         <v>3.12</v>
       </c>
       <c r="B314">
-        <v>0.08581730769230768</v>
+        <v>0.06865384615384615</v>
       </c>
       <c r="C314">
-        <v>0.24519230769230768</v>
+        <v>0.19615384615384615</v>
       </c>
       <c r="D314">
-        <v>0.3677884615384615</v>
+        <v>0.29423076923076924</v>
       </c>
     </row>
     <row r="315">
@@ -4419,13 +4419,13 @@
         <v>3.13</v>
       </c>
       <c r="B315">
-        <v>0.08554313099041533</v>
+        <v>0.06843450479233226</v>
       </c>
       <c r="C315">
-        <v>0.24440894568690097</v>
+        <v>0.19552715654952077</v>
       </c>
       <c r="D315">
-        <v>0.36661341853035145</v>
+        <v>0.29329073482428114</v>
       </c>
     </row>
     <row r="316">
@@ -4433,13 +4433,13 @@
         <v>3.14</v>
       </c>
       <c r="B316">
-        <v>0.08527070063694267</v>
+        <v>0.06821656050955413</v>
       </c>
       <c r="C316">
-        <v>0.24363057324840764</v>
+        <v>0.1949044585987261</v>
       </c>
       <c r="D316">
-        <v>0.36544585987261147</v>
+        <v>0.29235668789808916</v>
       </c>
     </row>
     <row r="317">
@@ -4447,13 +4447,13 @@
         <v>3.15</v>
       </c>
       <c r="B317">
-        <v>0.08499999999999999</v>
+        <v>0.06799999999999999</v>
       </c>
       <c r="C317">
-        <v>0.24285714285714285</v>
+        <v>0.19428571428571428</v>
       </c>
       <c r="D317">
-        <v>0.36428571428571427</v>
+        <v>0.2914285714285714</v>
       </c>
     </row>
     <row r="318">
@@ -4461,13 +4461,13 @@
         <v>3.16</v>
       </c>
       <c r="B318">
-        <v>0.08473101265822784</v>
+        <v>0.06778481012658226</v>
       </c>
       <c r="C318">
-        <v>0.2420886075949367</v>
+        <v>0.19367088607594934</v>
       </c>
       <c r="D318">
-        <v>0.36313291139240506</v>
+        <v>0.29050632911392404</v>
       </c>
     </row>
     <row r="319">
@@ -4475,13 +4475,13 @@
         <v>3.17</v>
       </c>
       <c r="B319">
-        <v>0.08446372239747633</v>
+        <v>0.06757097791798107</v>
       </c>
       <c r="C319">
-        <v>0.24132492113564669</v>
+        <v>0.19305993690851736</v>
       </c>
       <c r="D319">
-        <v>0.36198738170347</v>
+        <v>0.28958990536277607</v>
       </c>
     </row>
     <row r="320">
@@ -4489,13 +4489,13 @@
         <v>3.18</v>
       </c>
       <c r="B320">
-        <v>0.08419811320754716</v>
+        <v>0.06735849056603772</v>
       </c>
       <c r="C320">
-        <v>0.24056603773584906</v>
+        <v>0.19245283018867923</v>
       </c>
       <c r="D320">
-        <v>0.3608490566037736</v>
+        <v>0.28867924528301886</v>
       </c>
     </row>
     <row r="321">
@@ -4503,13 +4503,13 @@
         <v>3.19</v>
       </c>
       <c r="B321">
-        <v>0.08393416927899686</v>
+        <v>0.0671473354231975</v>
       </c>
       <c r="C321">
-        <v>0.23981191222570533</v>
+        <v>0.19184952978056427</v>
       </c>
       <c r="D321">
-        <v>0.359717868338558</v>
+        <v>0.2877742946708464</v>
       </c>
     </row>
     <row r="322">
@@ -4517,13 +4517,13 @@
         <v>3.2</v>
       </c>
       <c r="B322">
-        <v>0.08367187499999999</v>
+        <v>0.06693749999999998</v>
       </c>
       <c r="C322">
-        <v>0.23906249999999998</v>
+        <v>0.19124999999999998</v>
       </c>
       <c r="D322">
-        <v>0.35859375</v>
+        <v>0.286875</v>
       </c>
     </row>
     <row r="323">
@@ -4531,13 +4531,13 @@
         <v>3.21</v>
       </c>
       <c r="B323">
-        <v>0.08341121495327103</v>
+        <v>0.06672897196261682</v>
       </c>
       <c r="C323">
-        <v>0.2383177570093458</v>
+        <v>0.19065420560747665</v>
       </c>
       <c r="D323">
-        <v>0.3574766355140187</v>
+        <v>0.28598130841121494</v>
       </c>
     </row>
     <row r="324">
@@ -4545,13 +4545,13 @@
         <v>3.22</v>
       </c>
       <c r="B324">
-        <v>0.08315217391304347</v>
+        <v>0.06652173913043477</v>
       </c>
       <c r="C324">
-        <v>0.23757763975155277</v>
+        <v>0.19006211180124222</v>
       </c>
       <c r="D324">
-        <v>0.35636645962732916</v>
+        <v>0.2850931677018633</v>
       </c>
     </row>
     <row r="325">
@@ -4559,13 +4559,13 @@
         <v>3.23</v>
       </c>
       <c r="B325">
-        <v>0.08289473684210526</v>
+        <v>0.0663157894736842</v>
       </c>
       <c r="C325">
-        <v>0.2368421052631579</v>
+        <v>0.18947368421052632</v>
       </c>
       <c r="D325">
-        <v>0.35526315789473684</v>
+        <v>0.28421052631578947</v>
       </c>
     </row>
     <row r="326">
@@ -4573,13 +4573,13 @@
         <v>3.24</v>
       </c>
       <c r="B326">
-        <v>0.08263888888888889</v>
+        <v>0.0661111111111111</v>
       </c>
       <c r="C326">
-        <v>0.2361111111111111</v>
+        <v>0.18888888888888888</v>
       </c>
       <c r="D326">
-        <v>0.35416666666666663</v>
+        <v>0.2833333333333333</v>
       </c>
     </row>
     <row r="327">
@@ -4587,13 +4587,13 @@
         <v>3.25</v>
       </c>
       <c r="B327">
-        <v>0.08238461538461538</v>
+        <v>0.0659076923076923</v>
       </c>
       <c r="C327">
-        <v>0.2353846153846154</v>
+        <v>0.18830769230769231</v>
       </c>
       <c r="D327">
-        <v>0.35307692307692307</v>
+        <v>0.2824615384615385</v>
       </c>
     </row>
     <row r="328">
@@ -4601,13 +4601,13 @@
         <v>3.26</v>
       </c>
       <c r="B328">
-        <v>0.08213190184049081</v>
+        <v>0.06570552147239263</v>
       </c>
       <c r="C328">
-        <v>0.2346625766871166</v>
+        <v>0.18773006134969325</v>
       </c>
       <c r="D328">
-        <v>0.35199386503067487</v>
+        <v>0.28159509202453986</v>
       </c>
     </row>
     <row r="329">
@@ -4615,13 +4615,13 @@
         <v>3.27</v>
       </c>
       <c r="B329">
-        <v>0.08188073394495413</v>
+        <v>0.06550458715596329</v>
       </c>
       <c r="C329">
-        <v>0.23394495412844038</v>
+        <v>0.18715596330275228</v>
       </c>
       <c r="D329">
-        <v>0.35091743119266056</v>
+        <v>0.2807339449541284</v>
       </c>
     </row>
     <row r="330">
@@ -4629,13 +4629,13 @@
         <v>3.28</v>
       </c>
       <c r="B330">
-        <v>0.08163109756097561</v>
+        <v>0.06530487804878049</v>
       </c>
       <c r="C330">
-        <v>0.23323170731707318</v>
+        <v>0.18658536585365854</v>
       </c>
       <c r="D330">
-        <v>0.34984756097560976</v>
+        <v>0.27987804878048783</v>
       </c>
     </row>
     <row r="331">
@@ -4643,13 +4643,13 @@
         <v>3.29</v>
       </c>
       <c r="B331">
-        <v>0.08138297872340425</v>
+        <v>0.0651063829787234</v>
       </c>
       <c r="C331">
-        <v>0.23252279635258358</v>
+        <v>0.18601823708206686</v>
       </c>
       <c r="D331">
-        <v>0.3487841945288754</v>
+        <v>0.27902735562310027</v>
       </c>
     </row>
     <row r="332">
@@ -4657,13 +4657,13 @@
         <v>3.3</v>
       </c>
       <c r="B332">
-        <v>0.08113636363636365</v>
+        <v>0.0649090909090909</v>
       </c>
       <c r="C332">
-        <v>0.23181818181818184</v>
+        <v>0.18545454545454546</v>
       </c>
       <c r="D332">
-        <v>0.3477272727272728</v>
+        <v>0.2781818181818182</v>
       </c>
     </row>
     <row r="333">
@@ -4671,13 +4671,13 @@
         <v>3.31</v>
       </c>
       <c r="B333">
-        <v>0.08089123867069485</v>
+        <v>0.06471299093655589</v>
       </c>
       <c r="C333">
-        <v>0.2311178247734139</v>
+        <v>0.18489425981873112</v>
       </c>
       <c r="D333">
-        <v>0.3466767371601208</v>
+        <v>0.2773413897280967</v>
       </c>
     </row>
     <row r="334">
@@ -4685,13 +4685,13 @@
         <v>3.32</v>
       </c>
       <c r="B334">
-        <v>0.08064759036144578</v>
+        <v>0.06451807228915662</v>
       </c>
       <c r="C334">
-        <v>0.23042168674698796</v>
+        <v>0.18433734939759036</v>
       </c>
       <c r="D334">
-        <v>0.34563253012048195</v>
+        <v>0.2765060240963855</v>
       </c>
     </row>
     <row r="335">
@@ -4699,13 +4699,13 @@
         <v>3.33</v>
       </c>
       <c r="B335">
-        <v>0.0804054054054054</v>
+        <v>0.06432432432432432</v>
       </c>
       <c r="C335">
-        <v>0.22972972972972974</v>
+        <v>0.18378378378378377</v>
       </c>
       <c r="D335">
-        <v>0.3445945945945946</v>
+        <v>0.27567567567567564</v>
       </c>
     </row>
     <row r="336">
@@ -4713,13 +4713,13 @@
         <v>3.34</v>
       </c>
       <c r="B336">
-        <v>0.08016467065868263</v>
+        <v>0.0641317365269461</v>
       </c>
       <c r="C336">
-        <v>0.22904191616766467</v>
+        <v>0.18323353293413175</v>
       </c>
       <c r="D336">
-        <v>0.343562874251497</v>
+        <v>0.27485029940119765</v>
       </c>
     </row>
     <row r="337">
@@ -4727,13 +4727,13 @@
         <v>3.35</v>
       </c>
       <c r="B337">
-        <v>0.07992537313432835</v>
+        <v>0.06394029850746269</v>
       </c>
       <c r="C337">
-        <v>0.22835820895522388</v>
+        <v>0.1826865671641791</v>
       </c>
       <c r="D337">
-        <v>0.34253731343283583</v>
+        <v>0.2740298507462687</v>
       </c>
     </row>
     <row r="338">
@@ -4741,13 +4741,13 @@
         <v>3.36</v>
       </c>
       <c r="B338">
-        <v>0.07968750000000001</v>
+        <v>0.06374999999999999</v>
       </c>
       <c r="C338">
-        <v>0.22767857142857145</v>
+        <v>0.18214285714285713</v>
       </c>
       <c r="D338">
-        <v>0.3415178571428572</v>
+        <v>0.2732142857142857</v>
       </c>
     </row>
     <row r="339">
@@ -4755,13 +4755,13 @@
         <v>3.37</v>
       </c>
       <c r="B339">
-        <v>0.07945103857566764</v>
+        <v>0.06356083086053411</v>
       </c>
       <c r="C339">
-        <v>0.22700296735905043</v>
+        <v>0.18160237388724035</v>
       </c>
       <c r="D339">
-        <v>0.34050445103857563</v>
+        <v>0.27240356083086054</v>
       </c>
     </row>
     <row r="340">
@@ -4769,13 +4769,13 @@
         <v>3.38</v>
       </c>
       <c r="B340">
-        <v>0.07921597633136095</v>
+        <v>0.06337278106508876</v>
       </c>
       <c r="C340">
-        <v>0.22633136094674558</v>
+        <v>0.18106508875739646</v>
       </c>
       <c r="D340">
-        <v>0.3394970414201184</v>
+        <v>0.2715976331360947</v>
       </c>
     </row>
     <row r="341">
@@ -4783,13 +4783,13 @@
         <v>3.39</v>
       </c>
       <c r="B341">
-        <v>0.07898230088495574</v>
+        <v>0.0631858407079646</v>
       </c>
       <c r="C341">
-        <v>0.22566371681415928</v>
+        <v>0.18053097345132743</v>
       </c>
       <c r="D341">
-        <v>0.3384955752212389</v>
+        <v>0.27079646017699116</v>
       </c>
     </row>
     <row r="342">
@@ -4797,13 +4797,13 @@
         <v>3.4</v>
       </c>
       <c r="B342">
-        <v>0.07875</v>
+        <v>0.063</v>
       </c>
       <c r="C342">
-        <v>0.225</v>
+        <v>0.18</v>
       </c>
       <c r="D342">
-        <v>0.3375</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="343">
@@ -4811,13 +4811,13 @@
         <v>3.41</v>
       </c>
       <c r="B343">
-        <v>0.0785190615835777</v>
+        <v>0.06281524926686216</v>
       </c>
       <c r="C343">
-        <v>0.22434017595307917</v>
+        <v>0.17947214076246334</v>
       </c>
       <c r="D343">
-        <v>0.33651026392961875</v>
+        <v>0.26920821114369503</v>
       </c>
     </row>
     <row r="344">
@@ -4825,13 +4825,13 @@
         <v>3.42</v>
       </c>
       <c r="B344">
-        <v>0.07828947368421052</v>
+        <v>0.06263157894736841</v>
       </c>
       <c r="C344">
-        <v>0.2236842105263158</v>
+        <v>0.17894736842105263</v>
       </c>
       <c r="D344">
-        <v>0.3355263157894737</v>
+        <v>0.26842105263157895</v>
       </c>
     </row>
     <row r="345">
@@ -4839,13 +4839,13 @@
         <v>3.43</v>
       </c>
       <c r="B345">
-        <v>0.07806122448979591</v>
+        <v>0.06244897959183673</v>
       </c>
       <c r="C345">
-        <v>0.2230320699708455</v>
+        <v>0.17842565597667637</v>
       </c>
       <c r="D345">
-        <v>0.33454810495626824</v>
+        <v>0.26763848396501455</v>
       </c>
     </row>
     <row r="346">
@@ -4853,13 +4853,13 @@
         <v>3.44</v>
       </c>
       <c r="B346">
-        <v>0.07783430232558139</v>
+        <v>0.06226744186046511</v>
       </c>
       <c r="C346">
-        <v>0.22238372093023256</v>
+        <v>0.17790697674418604</v>
       </c>
       <c r="D346">
-        <v>0.3335755813953488</v>
+        <v>0.26686046511627903</v>
       </c>
     </row>
     <row r="347">
@@ -4867,13 +4867,13 @@
         <v>3.45</v>
       </c>
       <c r="B347">
-        <v>0.0776086956521739</v>
+        <v>0.06208695652173912</v>
       </c>
       <c r="C347">
-        <v>0.2217391304347826</v>
+        <v>0.17739130434782607</v>
       </c>
       <c r="D347">
-        <v>0.3326086956521739</v>
+        <v>0.2660869565217391</v>
       </c>
     </row>
     <row r="348">
@@ -4881,13 +4881,13 @@
         <v>3.46</v>
       </c>
       <c r="B348">
-        <v>0.07738439306358381</v>
+        <v>0.06190751445086705</v>
       </c>
       <c r="C348">
-        <v>0.22109826589595377</v>
+        <v>0.176878612716763</v>
       </c>
       <c r="D348">
-        <v>0.3316473988439307</v>
+        <v>0.2653179190751445</v>
       </c>
     </row>
     <row r="349">
@@ -4895,13 +4895,13 @@
         <v>3.47</v>
       </c>
       <c r="B349">
-        <v>0.07716138328530259</v>
+        <v>0.06172910662824207</v>
       </c>
       <c r="C349">
-        <v>0.22046109510086453</v>
+        <v>0.17636887608069163</v>
       </c>
       <c r="D349">
-        <v>0.3306916426512968</v>
+        <v>0.26455331412103744</v>
       </c>
     </row>
     <row r="350">
@@ -4909,13 +4909,13 @@
         <v>3.48</v>
       </c>
       <c r="B350">
-        <v>0.07693965517241379</v>
+        <v>0.06155172413793103</v>
       </c>
       <c r="C350">
-        <v>0.21982758620689655</v>
+        <v>0.17586206896551723</v>
       </c>
       <c r="D350">
-        <v>0.3297413793103448</v>
+        <v>0.26379310344827583</v>
       </c>
     </row>
     <row r="351">
@@ -4923,13 +4923,13 @@
         <v>3.49</v>
       </c>
       <c r="B351">
-        <v>0.07671919770773637</v>
+        <v>0.0613753581661891</v>
       </c>
       <c r="C351">
-        <v>0.21919770773638966</v>
+        <v>0.17535816618911174</v>
       </c>
       <c r="D351">
-        <v>0.3287965616045845</v>
+        <v>0.2630372492836676</v>
       </c>
     </row>
     <row r="352">
@@ -4937,13 +4937,13 @@
         <v>3.5</v>
       </c>
       <c r="B352">
-        <v>0.0765</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="C352">
-        <v>0.21857142857142858</v>
+        <v>0.17485714285714285</v>
       </c>
       <c r="D352">
-        <v>0.32785714285714285</v>
+        <v>0.2622857142857143</v>
       </c>
     </row>
     <row r="353">
@@ -4951,13 +4951,13 @@
         <v>3.51</v>
       </c>
       <c r="B353">
-        <v>0.07628205128205129</v>
+        <v>0.06102564102564103</v>
       </c>
       <c r="C353">
-        <v>0.21794871794871798</v>
+        <v>0.17435897435897438</v>
       </c>
       <c r="D353">
-        <v>0.326923076923077</v>
+        <v>0.26153846153846155</v>
       </c>
     </row>
     <row r="354">
@@ -4965,13 +4965,13 @@
         <v>3.52</v>
       </c>
       <c r="B354">
-        <v>0.07606534090909091</v>
+        <v>0.06085227272727272</v>
       </c>
       <c r="C354">
-        <v>0.21732954545454547</v>
+        <v>0.17386363636363636</v>
       </c>
       <c r="D354">
-        <v>0.32599431818181823</v>
+        <v>0.26079545454545455</v>
       </c>
     </row>
     <row r="355">
@@ -4979,13 +4979,13 @@
         <v>3.53</v>
       </c>
       <c r="B355">
-        <v>0.07584985835694051</v>
+        <v>0.06067988668555241</v>
       </c>
       <c r="C355">
-        <v>0.21671388101983005</v>
+        <v>0.17337110481586404</v>
       </c>
       <c r="D355">
-        <v>0.3250708215297451</v>
+        <v>0.26005665722379606</v>
       </c>
     </row>
     <row r="356">
@@ -4993,13 +4993,13 @@
         <v>3.54</v>
       </c>
       <c r="B356">
-        <v>0.07563559322033898</v>
+        <v>0.06050847457627118</v>
       </c>
       <c r="C356">
-        <v>0.21610169491525424</v>
+        <v>0.17288135593220338</v>
       </c>
       <c r="D356">
-        <v>0.3241525423728814</v>
+        <v>0.2593220338983051</v>
       </c>
     </row>
     <row r="357">
@@ -5007,13 +5007,13 @@
         <v>3.55</v>
       </c>
       <c r="B357">
-        <v>0.07542253521126761</v>
+        <v>0.06033802816901408</v>
       </c>
       <c r="C357">
-        <v>0.2154929577464789</v>
+        <v>0.1723943661971831</v>
       </c>
       <c r="D357">
-        <v>0.3232394366197183</v>
+        <v>0.25859154929577466</v>
       </c>
     </row>
     <row r="358">
@@ -5021,13 +5021,13 @@
         <v>3.56</v>
       </c>
       <c r="B358">
-        <v>0.07521067415730337</v>
+        <v>0.06016853932584269</v>
       </c>
       <c r="C358">
-        <v>0.2148876404494382</v>
+        <v>0.17191011235955056</v>
       </c>
       <c r="D358">
-        <v>0.3223314606741573</v>
+        <v>0.25786516853932584</v>
       </c>
     </row>
     <row r="359">
@@ -5035,13 +5035,13 @@
         <v>3.57</v>
       </c>
       <c r="B359">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="C359">
-        <v>0.2142857142857143</v>
+        <v>0.17142857142857143</v>
       </c>
       <c r="D359">
-        <v>0.32142857142857145</v>
+        <v>0.2571428571428571</v>
       </c>
     </row>
     <row r="360">
@@ -5049,13 +5049,13 @@
         <v>3.58</v>
       </c>
       <c r="B360">
-        <v>0.07479050279329609</v>
+        <v>0.059832402234636865</v>
       </c>
       <c r="C360">
-        <v>0.21368715083798884</v>
+        <v>0.17094972067039105</v>
       </c>
       <c r="D360">
-        <v>0.32053072625698326</v>
+        <v>0.25642458100558657</v>
       </c>
     </row>
     <row r="361">
@@ -5063,13 +5063,13 @@
         <v>3.59</v>
       </c>
       <c r="B361">
-        <v>0.07458217270194986</v>
+        <v>0.059665738161559886</v>
       </c>
       <c r="C361">
-        <v>0.21309192200557103</v>
+        <v>0.17047353760445683</v>
       </c>
       <c r="D361">
-        <v>0.31963788300835655</v>
+        <v>0.25571030640668524</v>
       </c>
     </row>
     <row r="362">
@@ -5077,13 +5077,13 @@
         <v>3.6</v>
       </c>
       <c r="B362">
-        <v>0.074375</v>
+        <v>0.05949999999999999</v>
       </c>
       <c r="C362">
-        <v>0.2125</v>
+        <v>0.16999999999999998</v>
       </c>
       <c r="D362">
-        <v>0.31875</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="363">
@@ -5091,13 +5091,13 @@
         <v>3.61</v>
       </c>
       <c r="B363">
-        <v>0.07416897506925207</v>
+        <v>0.05933518005540166</v>
       </c>
       <c r="C363">
-        <v>0.21191135734072022</v>
+        <v>0.16952908587257617</v>
       </c>
       <c r="D363">
-        <v>0.31786703601108035</v>
+        <v>0.25429362880886425</v>
       </c>
     </row>
     <row r="364">
@@ -5105,13 +5105,13 @@
         <v>3.62</v>
       </c>
       <c r="B364">
-        <v>0.07396408839779005</v>
+        <v>0.05917127071823204</v>
       </c>
       <c r="C364">
-        <v>0.21132596685082872</v>
+        <v>0.16906077348066298</v>
       </c>
       <c r="D364">
-        <v>0.3169889502762431</v>
+        <v>0.2535911602209945</v>
       </c>
     </row>
     <row r="365">
@@ -5119,13 +5119,13 @@
         <v>3.63</v>
       </c>
       <c r="B365">
-        <v>0.0737603305785124</v>
+        <v>0.059008264462809906</v>
       </c>
       <c r="C365">
-        <v>0.21074380165289258</v>
+        <v>0.16859504132231404</v>
       </c>
       <c r="D365">
-        <v>0.31611570247933884</v>
+        <v>0.25289256198347104</v>
       </c>
     </row>
     <row r="366">
@@ -5133,13 +5133,13 @@
         <v>3.64</v>
       </c>
       <c r="B366">
-        <v>0.07355769230769231</v>
+        <v>0.05884615384615384</v>
       </c>
       <c r="C366">
-        <v>0.21016483516483517</v>
+        <v>0.16813186813186812</v>
       </c>
       <c r="D366">
-        <v>0.31524725274725274</v>
+        <v>0.2521978021978022</v>
       </c>
     </row>
     <row r="367">
@@ -5147,13 +5147,13 @@
         <v>3.65</v>
       </c>
       <c r="B367">
-        <v>0.07335616438356164</v>
+        <v>0.05868493150684931</v>
       </c>
       <c r="C367">
-        <v>0.2095890410958904</v>
+        <v>0.16767123287671232</v>
       </c>
       <c r="D367">
-        <v>0.31438356164383563</v>
+        <v>0.2515068493150685</v>
       </c>
     </row>
     <row r="368">
@@ -5161,13 +5161,13 @@
         <v>3.66</v>
       </c>
       <c r="B368">
-        <v>0.07315573770491803</v>
+        <v>0.05852459016393442</v>
       </c>
       <c r="C368">
-        <v>0.20901639344262293</v>
+        <v>0.16721311475409836</v>
       </c>
       <c r="D368">
-        <v>0.3135245901639344</v>
+        <v>0.25081967213114753</v>
       </c>
     </row>
     <row r="369">
@@ -5175,13 +5175,13 @@
         <v>3.67</v>
       </c>
       <c r="B369">
-        <v>0.07295640326975476</v>
+        <v>0.05836512261580381</v>
       </c>
       <c r="C369">
-        <v>0.20844686648501362</v>
+        <v>0.1667574931880109</v>
       </c>
       <c r="D369">
-        <v>0.3126702997275204</v>
+        <v>0.2501362397820163</v>
       </c>
     </row>
     <row r="370">
@@ -5189,13 +5189,13 @@
         <v>3.68</v>
       </c>
       <c r="B370">
-        <v>0.07275815217391304</v>
+        <v>0.05820652173913043</v>
       </c>
       <c r="C370">
-        <v>0.2078804347826087</v>
+        <v>0.16630434782608694</v>
       </c>
       <c r="D370">
-        <v>0.3118206521739131</v>
+        <v>0.2494565217391304</v>
       </c>
     </row>
     <row r="371">
@@ -5203,13 +5203,13 @@
         <v>3.69</v>
       </c>
       <c r="B371">
-        <v>0.07256097560975609</v>
+        <v>0.058048780487804874</v>
       </c>
       <c r="C371">
-        <v>0.20731707317073172</v>
+        <v>0.16585365853658537</v>
       </c>
       <c r="D371">
-        <v>0.3109756097560976</v>
+        <v>0.24878048780487805</v>
       </c>
     </row>
     <row r="372">
@@ -5217,13 +5217,13 @@
         <v>3.7</v>
       </c>
       <c r="B372">
-        <v>0.07236486486486486</v>
+        <v>0.05789189189189188</v>
       </c>
       <c r="C372">
-        <v>0.20675675675675675</v>
+        <v>0.16540540540540538</v>
       </c>
       <c r="D372">
-        <v>0.31013513513513513</v>
+        <v>0.24810810810810807</v>
       </c>
     </row>
     <row r="373">
@@ -5231,13 +5231,13 @@
         <v>3.71</v>
       </c>
       <c r="B373">
-        <v>0.07216981132075471</v>
+        <v>0.057735849056603776</v>
       </c>
       <c r="C373">
-        <v>0.20619946091644206</v>
+        <v>0.16495956873315365</v>
       </c>
       <c r="D373">
-        <v>0.3092991913746631</v>
+        <v>0.24743935309973047</v>
       </c>
     </row>
     <row r="374">
@@ -5245,13 +5245,13 @@
         <v>3.72</v>
       </c>
       <c r="B374">
-        <v>0.07197580645161289</v>
+        <v>0.05758064516129031</v>
       </c>
       <c r="C374">
-        <v>0.20564516129032256</v>
+        <v>0.16451612903225804</v>
       </c>
       <c r="D374">
-        <v>0.3084677419354839</v>
+        <v>0.24677419354838706</v>
       </c>
     </row>
     <row r="375">
@@ -5259,13 +5259,13 @@
         <v>3.73</v>
       </c>
       <c r="B375">
-        <v>0.07178284182305629</v>
+        <v>0.05742627345844504</v>
       </c>
       <c r="C375">
-        <v>0.20509383378016086</v>
+        <v>0.1640750670241287</v>
       </c>
       <c r="D375">
-        <v>0.30764075067024127</v>
+        <v>0.24611260053619305</v>
       </c>
     </row>
     <row r="376">
@@ -5273,13 +5273,13 @@
         <v>3.74</v>
       </c>
       <c r="B376">
-        <v>0.07159090909090908</v>
+        <v>0.05727272727272727</v>
       </c>
       <c r="C376">
-        <v>0.20454545454545453</v>
+        <v>0.16363636363636364</v>
       </c>
       <c r="D376">
-        <v>0.30681818181818177</v>
+        <v>0.24545454545454545</v>
       </c>
     </row>
     <row r="377">
@@ -5287,13 +5287,13 @@
         <v>3.75</v>
       </c>
       <c r="B377">
-        <v>0.0714</v>
+        <v>0.05711999999999999</v>
       </c>
       <c r="C377">
-        <v>0.20400000000000001</v>
+        <v>0.16319999999999998</v>
       </c>
       <c r="D377">
-        <v>0.30600000000000005</v>
+        <v>0.24479999999999996</v>
       </c>
     </row>
     <row r="378">
@@ -5301,13 +5301,13 @@
         <v>3.76</v>
       </c>
       <c r="B378">
-        <v>0.07121010638297873</v>
+        <v>0.05696808510638298</v>
       </c>
       <c r="C378">
-        <v>0.20345744680851066</v>
+        <v>0.16276595744680852</v>
       </c>
       <c r="D378">
-        <v>0.305186170212766</v>
+        <v>0.24414893617021277</v>
       </c>
     </row>
     <row r="379">
@@ -5315,13 +5315,13 @@
         <v>3.77</v>
       </c>
       <c r="B379">
-        <v>0.07102122015915119</v>
+        <v>0.05681697612732095</v>
       </c>
       <c r="C379">
-        <v>0.20291777188328913</v>
+        <v>0.1623342175066313</v>
       </c>
       <c r="D379">
-        <v>0.3043766578249337</v>
+        <v>0.24350132625994694</v>
       </c>
     </row>
     <row r="380">
@@ -5329,13 +5329,13 @@
         <v>3.78</v>
       </c>
       <c r="B380">
-        <v>0.07083333333333333</v>
+        <v>0.056666666666666664</v>
       </c>
       <c r="C380">
-        <v>0.20238095238095238</v>
+        <v>0.1619047619047619</v>
       </c>
       <c r="D380">
-        <v>0.3035714285714286</v>
+        <v>0.24285714285714288</v>
       </c>
     </row>
     <row r="381">
@@ -5343,13 +5343,13 @@
         <v>3.79</v>
       </c>
       <c r="B381">
-        <v>0.07064643799472295</v>
+        <v>0.056517150395778364</v>
       </c>
       <c r="C381">
-        <v>0.20184696569920846</v>
+        <v>0.16147757255936676</v>
       </c>
       <c r="D381">
-        <v>0.3027704485488127</v>
+        <v>0.24221635883905013</v>
       </c>
     </row>
     <row r="382">
@@ -5357,13 +5357,13 @@
         <v>3.8</v>
       </c>
       <c r="B382">
-        <v>0.07046052631578947</v>
+        <v>0.056368421052631575</v>
       </c>
       <c r="C382">
-        <v>0.20131578947368423</v>
+        <v>0.16105263157894736</v>
       </c>
       <c r="D382">
-        <v>0.30197368421052634</v>
+        <v>0.24157894736842106</v>
       </c>
     </row>
     <row r="383">
@@ -5371,13 +5371,13 @@
         <v>3.81</v>
       </c>
       <c r="B383">
-        <v>0.0702755905511811</v>
+        <v>0.05622047244094488</v>
       </c>
       <c r="C383">
-        <v>0.20078740157480315</v>
+        <v>0.16062992125984252</v>
       </c>
       <c r="D383">
-        <v>0.30118110236220474</v>
+        <v>0.24094488188976376</v>
       </c>
     </row>
     <row r="384">
@@ -5385,13 +5385,13 @@
         <v>3.82</v>
       </c>
       <c r="B384">
-        <v>0.07009162303664922</v>
+        <v>0.05607329842931937</v>
       </c>
       <c r="C384">
-        <v>0.20026178010471204</v>
+        <v>0.16020942408376965</v>
       </c>
       <c r="D384">
-        <v>0.30039267015706805</v>
+        <v>0.24031413612565447</v>
       </c>
     </row>
     <row r="385">
@@ -5399,13 +5399,13 @@
         <v>3.83</v>
       </c>
       <c r="B385">
-        <v>0.06990861618798955</v>
+        <v>0.05592689295039164</v>
       </c>
       <c r="C385">
-        <v>0.19973890339425587</v>
+        <v>0.1597911227154047</v>
       </c>
       <c r="D385">
-        <v>0.29960835509138384</v>
+        <v>0.23968668407310703</v>
       </c>
     </row>
     <row r="386">
@@ -5413,13 +5413,13 @@
         <v>3.84</v>
       </c>
       <c r="B386">
-        <v>0.06972656249999999</v>
+        <v>0.055781250000000004</v>
       </c>
       <c r="C386">
-        <v>0.19921875</v>
+        <v>0.15937500000000002</v>
       </c>
       <c r="D386">
-        <v>0.298828125</v>
+        <v>0.2390625</v>
       </c>
     </row>
     <row r="387">
@@ -5427,13 +5427,13 @@
         <v>3.85</v>
       </c>
       <c r="B387">
-        <v>0.06954545454545455</v>
+        <v>0.05563636363636362</v>
       </c>
       <c r="C387">
-        <v>0.1987012987012987</v>
+        <v>0.15896103896103894</v>
       </c>
       <c r="D387">
-        <v>0.29805194805194807</v>
+        <v>0.2384415584415584</v>
       </c>
     </row>
     <row r="388">
@@ -5441,13 +5441,13 @@
         <v>3.86</v>
       </c>
       <c r="B388">
-        <v>0.06936528497409326</v>
+        <v>0.05549222797927461</v>
       </c>
       <c r="C388">
-        <v>0.19818652849740934</v>
+        <v>0.15854922279792746</v>
       </c>
       <c r="D388">
-        <v>0.297279792746114</v>
+        <v>0.23782383419689118</v>
       </c>
     </row>
     <row r="389">
@@ -5455,13 +5455,13 @@
         <v>3.87</v>
       </c>
       <c r="B389">
-        <v>0.0691860465116279</v>
+        <v>0.05534883720930232</v>
       </c>
       <c r="C389">
-        <v>0.19767441860465115</v>
+        <v>0.15813953488372093</v>
       </c>
       <c r="D389">
-        <v>0.2965116279069767</v>
+        <v>0.2372093023255814</v>
       </c>
     </row>
     <row r="390">
@@ -5469,13 +5469,13 @@
         <v>3.88</v>
       </c>
       <c r="B390">
-        <v>0.06900773195876289</v>
+        <v>0.055206185567010305</v>
       </c>
       <c r="C390">
-        <v>0.19716494845360827</v>
+        <v>0.1577319587628866</v>
       </c>
       <c r="D390">
-        <v>0.29574742268041243</v>
+        <v>0.2365979381443299</v>
       </c>
     </row>
     <row r="391">
@@ -5483,13 +5483,13 @@
         <v>3.89</v>
       </c>
       <c r="B391">
-        <v>0.06883033419023135</v>
+        <v>0.05506426735218509</v>
       </c>
       <c r="C391">
-        <v>0.19665809768637532</v>
+        <v>0.15732647814910025</v>
       </c>
       <c r="D391">
-        <v>0.294987146529563</v>
+        <v>0.23598971722365036</v>
       </c>
     </row>
     <row r="392">
@@ -5497,13 +5497,13 @@
         <v>3.9</v>
       </c>
       <c r="B392">
-        <v>0.06865384615384615</v>
+        <v>0.054923076923076915</v>
       </c>
       <c r="C392">
-        <v>0.19615384615384615</v>
+        <v>0.15692307692307692</v>
       </c>
       <c r="D392">
-        <v>0.29423076923076924</v>
+        <v>0.23538461538461536</v>
       </c>
     </row>
     <row r="393">
@@ -5511,13 +5511,13 @@
         <v>3.91</v>
       </c>
       <c r="B393">
-        <v>0.06847826086956521</v>
+        <v>0.054782608695652164</v>
       </c>
       <c r="C393">
-        <v>0.1956521739130435</v>
+        <v>0.15652173913043477</v>
       </c>
       <c r="D393">
-        <v>0.29347826086956524</v>
+        <v>0.23478260869565215</v>
       </c>
     </row>
     <row r="394">
@@ -5525,13 +5525,13 @@
         <v>3.92</v>
       </c>
       <c r="B394">
-        <v>0.06830357142857142</v>
+        <v>0.054642857142857146</v>
       </c>
       <c r="C394">
-        <v>0.1951530612244898</v>
+        <v>0.15612244897959185</v>
       </c>
       <c r="D394">
-        <v>0.2927295918367347</v>
+        <v>0.2341836734693878</v>
       </c>
     </row>
     <row r="395">
@@ -5539,13 +5539,13 @@
         <v>3.93</v>
       </c>
       <c r="B395">
-        <v>0.0681297709923664</v>
+        <v>0.05450381679389313</v>
       </c>
       <c r="C395">
-        <v>0.1946564885496183</v>
+        <v>0.15572519083969466</v>
       </c>
       <c r="D395">
-        <v>0.2919847328244275</v>
+        <v>0.233587786259542</v>
       </c>
     </row>
     <row r="396">
@@ -5553,13 +5553,13 @@
         <v>3.94</v>
       </c>
       <c r="B396">
-        <v>0.06795685279187817</v>
+        <v>0.054365482233502536</v>
       </c>
       <c r="C396">
-        <v>0.19416243654822335</v>
+        <v>0.15532994923857868</v>
       </c>
       <c r="D396">
-        <v>0.29124365482233505</v>
+        <v>0.23299492385786802</v>
       </c>
     </row>
     <row r="397">
@@ -5567,13 +5567,13 @@
         <v>3.95</v>
       </c>
       <c r="B397">
-        <v>0.06778481012658227</v>
+        <v>0.05422784810126581</v>
       </c>
       <c r="C397">
-        <v>0.19367088607594937</v>
+        <v>0.15493670886075947</v>
       </c>
       <c r="D397">
-        <v>0.29050632911392404</v>
+        <v>0.2324050632911392</v>
       </c>
     </row>
     <row r="398">
@@ -5581,13 +5581,13 @@
         <v>3.96</v>
       </c>
       <c r="B398">
-        <v>0.06761363636363636</v>
+        <v>0.054090909090909085</v>
       </c>
       <c r="C398">
-        <v>0.19318181818181818</v>
+        <v>0.15454545454545454</v>
       </c>
       <c r="D398">
-        <v>0.2897727272727273</v>
+        <v>0.2318181818181818</v>
       </c>
     </row>
     <row r="399">
@@ -5595,13 +5595,13 @@
         <v>3.97</v>
       </c>
       <c r="B399">
-        <v>0.06744332493702769</v>
+        <v>0.053954659949622154</v>
       </c>
       <c r="C399">
-        <v>0.19269521410579343</v>
+        <v>0.15415617128463474</v>
       </c>
       <c r="D399">
-        <v>0.2890428211586902</v>
+        <v>0.2312342569269521</v>
       </c>
     </row>
     <row r="400">
@@ -5609,13 +5609,13 @@
         <v>3.98</v>
       </c>
       <c r="B400">
-        <v>0.06727386934673367</v>
+        <v>0.05381909547738693</v>
       </c>
       <c r="C400">
-        <v>0.1922110552763819</v>
+        <v>0.15376884422110554</v>
       </c>
       <c r="D400">
-        <v>0.28831658291457285</v>
+        <v>0.2306532663316583</v>
       </c>
     </row>
     <row r="401">
@@ -5623,13 +5623,13 @@
         <v>3.99</v>
       </c>
       <c r="B401">
-        <v>0.06710526315789472</v>
+        <v>0.053684210526315786</v>
       </c>
       <c r="C401">
-        <v>0.19172932330827067</v>
+        <v>0.15338345864661654</v>
       </c>
       <c r="D401">
-        <v>0.287593984962406</v>
+        <v>0.23007518796992482</v>
       </c>
     </row>
     <row r="402">
@@ -5637,13 +5637,13 @@
         <v>4.0</v>
       </c>
       <c r="B402">
-        <v>0.0669375</v>
+        <v>0.05354999999999999</v>
       </c>
       <c r="C402">
-        <v>0.19125</v>
+        <v>0.153</v>
       </c>
       <c r="D402">
-        <v>0.286875</v>
+        <v>0.22949999999999998</v>
       </c>
     </row>
     <row r="403">
@@ -5651,13 +5651,13 @@
         <v>4.01</v>
       </c>
       <c r="B403">
-        <v>0.06677057356608479</v>
+        <v>0.053416458852867825</v>
       </c>
       <c r="C403">
-        <v>0.19077306733167085</v>
+        <v>0.15261845386533665</v>
       </c>
       <c r="D403">
-        <v>0.28615960099750626</v>
+        <v>0.22892768079800496</v>
       </c>
     </row>
     <row r="404">
@@ -5665,13 +5665,13 @@
         <v>4.02</v>
       </c>
       <c r="B404">
-        <v>0.0666044776119403</v>
+        <v>0.053283582089552244</v>
       </c>
       <c r="C404">
-        <v>0.1902985074626866</v>
+        <v>0.15223880597014927</v>
       </c>
       <c r="D404">
-        <v>0.28544776119402987</v>
+        <v>0.2283582089552239</v>
       </c>
     </row>
     <row r="405">
@@ -5679,13 +5679,13 @@
         <v>4.03</v>
       </c>
       <c r="B405">
-        <v>0.06643920595533498</v>
+        <v>0.05315136476426798</v>
       </c>
       <c r="C405">
-        <v>0.18982630272952852</v>
+        <v>0.1518610421836228</v>
       </c>
       <c r="D405">
-        <v>0.2847394540942928</v>
+        <v>0.2277915632754342</v>
       </c>
     </row>
     <row r="406">
@@ -5693,13 +5693,13 @@
         <v>4.04</v>
       </c>
       <c r="B406">
-        <v>0.06627475247524751</v>
+        <v>0.05301980198019802</v>
       </c>
       <c r="C406">
-        <v>0.18935643564356436</v>
+        <v>0.15148514851485148</v>
       </c>
       <c r="D406">
-        <v>0.2840346534653465</v>
+        <v>0.2272277227722772</v>
       </c>
     </row>
     <row r="407">
@@ -5707,13 +5707,13 @@
         <v>4.05</v>
       </c>
       <c r="B407">
-        <v>0.06611111111111112</v>
+        <v>0.05288888888888889</v>
       </c>
       <c r="C407">
-        <v>0.1888888888888889</v>
+        <v>0.1511111111111111</v>
       </c>
       <c r="D407">
-        <v>0.2833333333333334</v>
+        <v>0.22666666666666668</v>
       </c>
     </row>
     <row r="408">
@@ -5721,13 +5721,13 @@
         <v>4.06</v>
       </c>
       <c r="B408">
-        <v>0.06594827586206897</v>
+        <v>0.05275862068965517</v>
       </c>
       <c r="C408">
-        <v>0.18842364532019706</v>
+        <v>0.15073891625615765</v>
       </c>
       <c r="D408">
-        <v>0.2826354679802956</v>
+        <v>0.22610837438423648</v>
       </c>
     </row>
     <row r="409">
@@ -5735,13 +5735,13 @@
         <v>4.07</v>
       </c>
       <c r="B409">
-        <v>0.06578624078624078</v>
+        <v>0.05262899262899262</v>
       </c>
       <c r="C409">
-        <v>0.18796068796068796</v>
+        <v>0.15036855036855035</v>
       </c>
       <c r="D409">
-        <v>0.2819410319410319</v>
+        <v>0.22555282555282552</v>
       </c>
     </row>
     <row r="410">
@@ -5749,13 +5749,13 @@
         <v>4.08</v>
       </c>
       <c r="B410">
-        <v>0.06562499999999999</v>
+        <v>0.0525</v>
       </c>
       <c r="C410">
-        <v>0.1875</v>
+        <v>0.15</v>
       </c>
       <c r="D410">
-        <v>0.28125</v>
+        <v>0.22499999999999998</v>
       </c>
     </row>
     <row r="411">
@@ -5763,13 +5763,13 @@
         <v>4.09</v>
       </c>
       <c r="B411">
-        <v>0.06530448765849081</v>
+        <v>0.052243590126792645</v>
       </c>
       <c r="C411">
-        <v>0.1865842504528309</v>
+        <v>0.1492674003622647</v>
       </c>
       <c r="D411">
-        <v>0.27987637567924634</v>
+        <v>0.22390110054339707</v>
       </c>
     </row>
     <row r="412">
@@ -5777,13 +5777,13 @@
         <v>4.1</v>
       </c>
       <c r="B412">
-        <v>0.06498631766805472</v>
+        <v>0.05198905413444378</v>
       </c>
       <c r="C412">
-        <v>0.18567519333729923</v>
+        <v>0.14854015466983939</v>
       </c>
       <c r="D412">
-        <v>0.27851279000594886</v>
+        <v>0.22281023200475908</v>
       </c>
     </row>
     <row r="413">
@@ -5791,13 +5791,13 @@
         <v>4.11</v>
       </c>
       <c r="B413">
-        <v>0.06467046725984334</v>
+        <v>0.05173637380787468</v>
       </c>
       <c r="C413">
-        <v>0.18477276359955241</v>
+        <v>0.14781821087964195</v>
       </c>
       <c r="D413">
-        <v>0.2771591453993286</v>
+        <v>0.2217273163194629</v>
       </c>
     </row>
     <row r="414">
@@ -5805,13 +5805,13 @@
         <v>4.12</v>
       </c>
       <c r="B414">
-        <v>0.0643569139409935</v>
+        <v>0.0514855311527948</v>
       </c>
       <c r="C414">
-        <v>0.18387689697426715</v>
+        <v>0.14710151757941373</v>
       </c>
       <c r="D414">
-        <v>0.27581534546140074</v>
+        <v>0.2206522763691206</v>
       </c>
     </row>
     <row r="415">
@@ -5819,13 +5819,13 @@
         <v>4.13</v>
       </c>
       <c r="B415">
-        <v>0.06404563549062256</v>
+        <v>0.051236508392498055</v>
       </c>
       <c r="C415">
-        <v>0.18298752997320733</v>
+        <v>0.14639002397856588</v>
       </c>
       <c r="D415">
-        <v>0.274481294959811</v>
+        <v>0.2195850359678488</v>
       </c>
     </row>
     <row r="416">
@@ -5833,13 +5833,13 @@
         <v>4.14</v>
       </c>
       <c r="B416">
-        <v>0.06373660995589162</v>
+        <v>0.050989287964713303</v>
       </c>
       <c r="C416">
-        <v>0.18210459987397606</v>
+        <v>0.14568367989918088</v>
       </c>
       <c r="D416">
-        <v>0.2731568998109641</v>
+        <v>0.21852551984877133</v>
       </c>
     </row>
     <row r="417">
@@ -5847,13 +5847,13 @@
         <v>4.15</v>
       </c>
       <c r="B417">
-        <v>0.06342981564813469</v>
+        <v>0.05074385251850776</v>
       </c>
       <c r="C417">
-        <v>0.18122804470895626</v>
+        <v>0.14498243576716502</v>
       </c>
       <c r="D417">
-        <v>0.2718420670634344</v>
+        <v>0.21747365365074753</v>
       </c>
     </row>
     <row r="418">
@@ -5861,13 +5861,13 @@
         <v>4.16</v>
       </c>
       <c r="B418">
-        <v>0.06312523113905325</v>
+        <v>0.05050018491124259</v>
       </c>
       <c r="C418">
-        <v>0.18035780325443784</v>
+        <v>0.14428624260355027</v>
       </c>
       <c r="D418">
-        <v>0.27053670488165676</v>
+        <v>0.2164293639053254</v>
       </c>
     </row>
     <row r="419">
@@ -5875,13 +5875,13 @@
         <v>4.17</v>
       </c>
       <c r="B419">
-        <v>0.06282283525697427</v>
+        <v>0.05025826820557942</v>
       </c>
       <c r="C419">
-        <v>0.1794938150199265</v>
+        <v>0.14359505201594122</v>
       </c>
       <c r="D419">
-        <v>0.26924072252988973</v>
+        <v>0.21539257802391182</v>
       </c>
     </row>
     <row r="420">
@@ -5889,13 +5889,13 @@
         <v>4.18</v>
       </c>
       <c r="B420">
-        <v>0.06252260708317117</v>
+        <v>0.05001808566653695</v>
       </c>
       <c r="C420">
-        <v>0.17863602023763195</v>
+        <v>0.14290881619010556</v>
       </c>
       <c r="D420">
-        <v>0.26795403035644794</v>
+        <v>0.21436322428515836</v>
       </c>
     </row>
     <row r="421">
@@ -5903,13 +5903,13 @@
         <v>4.19</v>
       </c>
       <c r="B421">
-        <v>0.06222452594824589</v>
+        <v>0.04977962075859672</v>
       </c>
       <c r="C421">
-        <v>0.17778435985213112</v>
+        <v>0.14222748788170492</v>
       </c>
       <c r="D421">
-        <v>0.26667653977819666</v>
+        <v>0.21334123182255738</v>
       </c>
     </row>
     <row r="422">
@@ -5917,13 +5917,13 @@
         <v>4.2</v>
       </c>
       <c r="B422">
-        <v>0.061928571428571416</v>
+        <v>0.04954285714285714</v>
       </c>
       <c r="C422">
-        <v>0.17693877551020407</v>
+        <v>0.14155102040816325</v>
       </c>
       <c r="D422">
-        <v>0.2654081632653061</v>
+        <v>0.21232653061224488</v>
       </c>
     </row>
     <row r="423">
@@ -5931,13 +5931,13 @@
         <v>4.21</v>
       </c>
       <c r="B423">
-        <v>0.061634723342793137</v>
+        <v>0.04930777867423451</v>
       </c>
       <c r="C423">
-        <v>0.17609920955083755</v>
+        <v>0.14087936764067005</v>
       </c>
       <c r="D423">
-        <v>0.2641488143262563</v>
+        <v>0.21131905146100508</v>
       </c>
     </row>
     <row r="424">
@@ -5945,13 +5945,13 @@
         <v>4.22</v>
       </c>
       <c r="B424">
-        <v>0.0613429617483884</v>
+        <v>0.049074369398710724</v>
       </c>
       <c r="C424">
-        <v>0.17526560499539545</v>
+        <v>0.14021248399631636</v>
       </c>
       <c r="D424">
-        <v>0.2628984074930932</v>
+        <v>0.21031872599447454</v>
       </c>
     </row>
     <row r="425">
@@ -5959,13 +5959,13 @@
         <v>4.23</v>
       </c>
       <c r="B425">
-        <v>0.061053266938282766</v>
+        <v>0.04884261355062621</v>
       </c>
       <c r="C425">
-        <v>0.17443790553795077</v>
+        <v>0.1395503244303606</v>
       </c>
       <c r="D425">
-        <v>0.26165685830692614</v>
+        <v>0.2093254866455409</v>
       </c>
     </row>
     <row r="426">
@@ -5973,13 +5973,13 @@
         <v>4.24</v>
       </c>
       <c r="B426">
-        <v>0.060765619437522234</v>
+        <v>0.04861249555001779</v>
       </c>
       <c r="C426">
-        <v>0.17361605553577783</v>
+        <v>0.13889284442862226</v>
       </c>
       <c r="D426">
-        <v>0.26042408330366673</v>
+        <v>0.2083392666429334</v>
       </c>
     </row>
     <row r="427">
@@ -5987,13 +5987,13 @@
         <v>4.25</v>
       </c>
       <c r="B427">
-        <v>0.06048</v>
+        <v>0.048383999999999996</v>
       </c>
       <c r="C427">
-        <v>0.1728</v>
+        <v>0.13824</v>
       </c>
       <c r="D427">
-        <v>0.2592</v>
+        <v>0.20736</v>
       </c>
     </row>
     <row r="428">
@@ -6001,13 +6001,13 @@
         <v>4.26</v>
       </c>
       <c r="B428">
-        <v>0.06019638960523706</v>
+        <v>0.04815711168418965</v>
       </c>
       <c r="C428">
-        <v>0.1719896845863916</v>
+        <v>0.1375917476691133</v>
       </c>
       <c r="D428">
-        <v>0.2579845268795874</v>
+        <v>0.20638762150366996</v>
       </c>
     </row>
     <row r="429">
@@ -6015,13 +6015,13 @@
         <v>4.27</v>
       </c>
       <c r="B429">
-        <v>0.05991476945521558</v>
+        <v>0.04793181556417247</v>
       </c>
       <c r="C429">
-        <v>0.17118505558633024</v>
+        <v>0.1369480444690642</v>
       </c>
       <c r="D429">
-        <v>0.25677758337949536</v>
+        <v>0.2054220667035963</v>
       </c>
     </row>
     <row r="430">
@@ -6029,13 +6029,13 @@
         <v>4.28</v>
       </c>
       <c r="B430">
-        <v>0.05963512097126386</v>
+        <v>0.04770809677701109</v>
       </c>
       <c r="C430">
-        <v>0.17038605991789676</v>
+        <v>0.1363088479343174</v>
       </c>
       <c r="D430">
-        <v>0.25557908987684513</v>
+        <v>0.20446327190147612</v>
       </c>
     </row>
     <row r="431">
@@ -6043,13 +6043,13 @@
         <v>4.29</v>
       </c>
       <c r="B431">
-        <v>0.059357425790992215</v>
+        <v>0.04748594063279377</v>
       </c>
       <c r="C431">
-        <v>0.16959264511712063</v>
+        <v>0.1356741160936965</v>
       </c>
       <c r="D431">
-        <v>0.254388967675681</v>
+        <v>0.20351117414054476</v>
       </c>
     </row>
     <row r="432">
@@ -6057,13 +6057,13 @@
         <v>4.3</v>
       </c>
       <c r="B432">
-        <v>0.05908166576527853</v>
+        <v>0.04726533261222282</v>
       </c>
       <c r="C432">
-        <v>0.16880475932936723</v>
+        <v>0.1350438074634938</v>
       </c>
       <c r="D432">
-        <v>0.25320713899405084</v>
+        <v>0.2025657111952407</v>
       </c>
     </row>
     <row r="433">
@@ -6071,13 +6071,13 @@
         <v>4.31</v>
       </c>
       <c r="B433">
-        <v>0.05880782295530279</v>
+        <v>0.047046258364242234</v>
       </c>
       <c r="C433">
-        <v>0.16802235130086512</v>
+        <v>0.1344178810406921</v>
       </c>
       <c r="D433">
-        <v>0.25203352695129766</v>
+        <v>0.20162682156103817</v>
       </c>
     </row>
     <row r="434">
@@ -6085,13 +6085,13 @@
         <v>4.32</v>
       </c>
       <c r="B434">
-        <v>0.05853587962962962</v>
+        <v>0.04682870370370369</v>
       </c>
       <c r="C434">
-        <v>0.16724537037037035</v>
+        <v>0.13379629629629627</v>
       </c>
       <c r="D434">
-        <v>0.2508680555555555</v>
+        <v>0.2006944444444444</v>
       </c>
     </row>
     <row r="435">
@@ -6099,13 +6099,13 @@
         <v>4.33</v>
       </c>
       <c r="B435">
-        <v>0.05826581826133799</v>
+        <v>0.0466126546090704</v>
       </c>
       <c r="C435">
-        <v>0.1664737664609657</v>
+        <v>0.1331790131687726</v>
       </c>
       <c r="D435">
-        <v>0.24971064969144857</v>
+        <v>0.1997685197531589</v>
       </c>
     </row>
     <row r="436">
@@ -6113,13 +6113,13 @@
         <v>4.34</v>
       </c>
       <c r="B436">
-        <v>0.05799762152519697</v>
+        <v>0.04639809722015757</v>
       </c>
       <c r="C436">
-        <v>0.16570749007199134</v>
+        <v>0.13256599205759306</v>
       </c>
       <c r="D436">
-        <v>0.248561235107987</v>
+        <v>0.1988489880863896</v>
       </c>
     </row>
     <row r="437">
@@ -6127,13 +6127,13 @@
         <v>4.35</v>
       </c>
       <c r="B437">
-        <v>0.057731272294887045</v>
+        <v>0.04618501783590964</v>
       </c>
       <c r="C437">
-        <v>0.16494649227110586</v>
+        <v>0.1319571938168847</v>
       </c>
       <c r="D437">
-        <v>0.2474197384066588</v>
+        <v>0.19793579072532705</v>
       </c>
     </row>
     <row r="438">
@@ -6141,13 +6141,13 @@
         <v>4.36</v>
       </c>
       <c r="B438">
-        <v>0.05746675364026596</v>
+        <v>0.045973402912212774</v>
       </c>
       <c r="C438">
-        <v>0.1641907246864742</v>
+        <v>0.13135257974917935</v>
       </c>
       <c r="D438">
-        <v>0.24628608702971128</v>
+        <v>0.19702886962376903</v>
       </c>
     </row>
     <row r="439">
@@ -6155,13 +6155,13 @@
         <v>4.37</v>
       </c>
       <c r="B439">
-        <v>0.05720404882467834</v>
+        <v>0.04576323905974268</v>
       </c>
       <c r="C439">
-        <v>0.16344013949908098</v>
+        <v>0.1307521115992648</v>
       </c>
       <c r="D439">
-        <v>0.24516020924862147</v>
+        <v>0.1961281673988972</v>
       </c>
     </row>
     <row r="440">
@@ -6169,13 +6169,13 @@
         <v>4.38</v>
       </c>
       <c r="B440">
-        <v>0.05694314130230812</v>
+        <v>0.045554513041846496</v>
       </c>
       <c r="C440">
-        <v>0.16269468943516607</v>
+        <v>0.13015575154813286</v>
       </c>
       <c r="D440">
-        <v>0.2440420341527491</v>
+        <v>0.1952336273221993</v>
       </c>
     </row>
     <row r="441">
@@ -6183,13 +6183,13 @@
         <v>4.39</v>
       </c>
       <c r="B441">
-        <v>0.05668401471557329</v>
+        <v>0.04534721177245863</v>
       </c>
       <c r="C441">
-        <v>0.16195432775878085</v>
+        <v>0.12956346220702467</v>
       </c>
       <c r="D441">
-        <v>0.2429314916381713</v>
+        <v>0.194345193310537</v>
       </c>
     </row>
     <row r="442">
@@ -6197,13 +6197,13 @@
         <v>4.4</v>
       </c>
       <c r="B442">
-        <v>0.05642665289256197</v>
+        <v>0.045141322314049576</v>
       </c>
       <c r="C442">
-        <v>0.16121900826446278</v>
+        <v>0.12897520661157022</v>
       </c>
       <c r="D442">
-        <v>0.24182851239669417</v>
+        <v>0.19346280991735532</v>
       </c>
     </row>
     <row r="443">
@@ -6211,13 +6211,13 @@
         <v>4.41</v>
       </c>
       <c r="B443">
-        <v>0.05617103984450923</v>
+        <v>0.04493683187560738</v>
       </c>
       <c r="C443">
-        <v>0.16048868527002638</v>
+        <v>0.1283909482160211</v>
       </c>
       <c r="D443">
-        <v>0.2407330279050396</v>
+        <v>0.19258642232403164</v>
       </c>
     </row>
     <row r="444">
@@ -6225,13 +6225,13 @@
         <v>4.42</v>
       </c>
       <c r="B444">
-        <v>0.0559171597633136</v>
+        <v>0.04473372781065088</v>
       </c>
       <c r="C444">
-        <v>0.15976331360946744</v>
+        <v>0.12781065088757396</v>
       </c>
       <c r="D444">
-        <v>0.23964497041420116</v>
+        <v>0.19171597633136095</v>
       </c>
     </row>
     <row r="445">
@@ -6239,13 +6239,13 @@
         <v>4.43</v>
       </c>
       <c r="B445">
-        <v>0.055664997019093096</v>
+        <v>0.04453199761527448</v>
       </c>
       <c r="C445">
-        <v>0.15904284862598028</v>
+        <v>0.12723427890078423</v>
       </c>
       <c r="D445">
-        <v>0.23856427293897042</v>
+        <v>0.19085141835117636</v>
       </c>
     </row>
     <row r="446">
@@ -6253,13 +6253,13 @@
         <v>4.44</v>
       </c>
       <c r="B446">
-        <v>0.05541453615777939</v>
+        <v>0.04433162892622351</v>
       </c>
       <c r="C446">
-        <v>0.15832724616508398</v>
+        <v>0.1266617969320672</v>
       </c>
       <c r="D446">
-        <v>0.23749086924762597</v>
+        <v>0.1899926953981008</v>
       </c>
     </row>
     <row r="447">
@@ -6267,13 +6267,13 @@
         <v>4.45</v>
       </c>
       <c r="B447">
-        <v>0.05516576189875015</v>
+        <v>0.04413260951900012</v>
       </c>
       <c r="C447">
-        <v>0.15761646256785758</v>
+        <v>0.12609317005428605</v>
       </c>
       <c r="D447">
-        <v>0.23642469385178638</v>
+        <v>0.18913975508142908</v>
       </c>
     </row>
     <row r="448">
@@ -6281,13 +6281,13 @@
         <v>4.46</v>
       </c>
       <c r="B448">
-        <v>0.05491865913249813</v>
+        <v>0.04393492730599851</v>
       </c>
       <c r="C448">
-        <v>0.15691045466428039</v>
+        <v>0.12552836373142431</v>
       </c>
       <c r="D448">
-        <v>0.23536568199642058</v>
+        <v>0.18829254559713648</v>
       </c>
     </row>
     <row r="449">
@@ -6295,13 +6295,13 @@
         <v>4.47</v>
       </c>
       <c r="B449">
-        <v>0.054673212918337016</v>
+        <v>0.04373857033466961</v>
       </c>
       <c r="C449">
-        <v>0.1562091797666772</v>
+        <v>0.12496734381334175</v>
       </c>
       <c r="D449">
-        <v>0.2343137696500158</v>
+        <v>0.18745101572001263</v>
       </c>
     </row>
     <row r="450">
@@ -6309,13 +6309,13 @@
         <v>4.48</v>
       </c>
       <c r="B450">
-        <v>0.054429408482142845</v>
+        <v>0.04354352678571428</v>
       </c>
       <c r="C450">
-        <v>0.15551259566326528</v>
+        <v>0.12441007653061223</v>
       </c>
       <c r="D450">
-        <v>0.23326889349489793</v>
+        <v>0.18661511479591836</v>
       </c>
     </row>
     <row r="451">
@@ -6323,13 +6323,13 @@
         <v>4.49</v>
       </c>
       <c r="B451">
-        <v>0.05418723121413087</v>
+        <v>0.0433497849713047</v>
       </c>
       <c r="C451">
-        <v>0.1548206606118025</v>
+        <v>0.123856528489442</v>
       </c>
       <c r="D451">
-        <v>0.23223099091770374</v>
+        <v>0.18578479273416298</v>
       </c>
     </row>
     <row r="452">
@@ -6337,13 +6337,13 @@
         <v>4.5</v>
       </c>
       <c r="B452">
-        <v>0.05394666666666667</v>
+        <v>0.04315733333333333</v>
       </c>
       <c r="C452">
-        <v>0.15413333333333334</v>
+        <v>0.12330666666666668</v>
       </c>
       <c r="D452">
-        <v>0.23120000000000002</v>
+        <v>0.18496</v>
       </c>
     </row>
     <row r="453">
@@ -6351,13 +6351,13 @@
         <v>4.51</v>
       </c>
       <c r="B453">
-        <v>0.05370770055211135</v>
+        <v>0.04296616044168908</v>
       </c>
       <c r="C453">
-        <v>0.15345057300603243</v>
+        <v>0.12276045840482594</v>
       </c>
       <c r="D453">
-        <v>0.23017585950904865</v>
+        <v>0.1841406876072389</v>
       </c>
     </row>
     <row r="454">
@@ -6365,13 +6365,13 @@
         <v>4.52</v>
       </c>
       <c r="B454">
-        <v>0.05347031874070014</v>
+        <v>0.04277625499256012</v>
       </c>
       <c r="C454">
-        <v>0.15277233925914327</v>
+        <v>0.12221787140731462</v>
       </c>
       <c r="D454">
-        <v>0.22915850888871492</v>
+        <v>0.18332680711097193</v>
       </c>
     </row>
     <row r="455">
@@ -6379,13 +6379,13 @@
         <v>4.53</v>
       </c>
       <c r="B455">
-        <v>0.05323450725845357</v>
+        <v>0.04258760580676286</v>
       </c>
       <c r="C455">
-        <v>0.15209859216701022</v>
+        <v>0.12167887373360817</v>
       </c>
       <c r="D455">
-        <v>0.22814788825051532</v>
+        <v>0.18251831060041224</v>
       </c>
     </row>
     <row r="456">
@@ -6393,13 +6393,13 @@
         <v>4.54</v>
       </c>
       <c r="B456">
-        <v>0.053000252285121</v>
+        <v>0.042400201828096805</v>
       </c>
       <c r="C456">
-        <v>0.15142929224320287</v>
+        <v>0.1211434337945623</v>
       </c>
       <c r="D456">
-        <v>0.2271439383648043</v>
+        <v>0.18171515069184346</v>
       </c>
     </row>
     <row r="457">
@@ -6407,13 +6407,13 @@
         <v>4.55</v>
       </c>
       <c r="B457">
-        <v>0.05276754015215555</v>
+        <v>0.042214032121724435</v>
       </c>
       <c r="C457">
-        <v>0.15076440043473013</v>
+        <v>0.1206115203477841</v>
       </c>
       <c r="D457">
-        <v>0.2261466006520952</v>
+        <v>0.18091728052167616</v>
       </c>
     </row>
     <row r="458">
@@ -6421,13 +6421,13 @@
         <v>4.56</v>
       </c>
       <c r="B458">
-        <v>0.05253635734072023</v>
+        <v>0.042029085872576186</v>
       </c>
       <c r="C458">
-        <v>0.15010387811634351</v>
+        <v>0.12008310249307481</v>
       </c>
       <c r="D458">
-        <v>0.22515581717451527</v>
+        <v>0.18012465373961223</v>
       </c>
     </row>
     <row r="459">
@@ -6435,13 +6435,13 @@
         <v>4.57</v>
       </c>
       <c r="B459">
-        <v>0.052306690479724575</v>
+        <v>0.04184535238377966</v>
       </c>
       <c r="C459">
-        <v>0.14944768708492737</v>
+        <v>0.1195581496679419</v>
       </c>
       <c r="D459">
-        <v>0.22417153062739104</v>
+        <v>0.17933722450191286</v>
       </c>
     </row>
     <row r="460">
@@ -6449,13 +6449,13 @@
         <v>4.58</v>
       </c>
       <c r="B460">
-        <v>0.05207852634389122</v>
+        <v>0.04166282107511298</v>
       </c>
       <c r="C460">
-        <v>0.14879578955397493</v>
+        <v>0.11903663164317994</v>
       </c>
       <c r="D460">
-        <v>0.2231936843309624</v>
+        <v>0.1785549474647699</v>
       </c>
     </row>
     <row r="461">
@@ -6463,13 +6463,13 @@
         <v>4.59</v>
       </c>
       <c r="B461">
-        <v>0.05185185185185186</v>
+        <v>0.04148148148148149</v>
       </c>
       <c r="C461">
-        <v>0.14814814814814817</v>
+        <v>0.11851851851851854</v>
       </c>
       <c r="D461">
-        <v>0.22222222222222227</v>
+        <v>0.1777777777777778</v>
       </c>
     </row>
     <row r="462">
@@ -6477,13 +6477,13 @@
         <v>4.6</v>
       </c>
       <c r="B462">
-        <v>0.05162665406427222</v>
+        <v>0.041301323251417776</v>
       </c>
       <c r="C462">
-        <v>0.14750472589792063</v>
+        <v>0.1180037807183365</v>
       </c>
       <c r="D462">
-        <v>0.22125708884688094</v>
+        <v>0.17700567107750476</v>
       </c>
     </row>
     <row r="463">
@@ -6491,13 +6491,13 @@
         <v>4.61</v>
       </c>
       <c r="B463">
-        <v>0.05140292018200553</v>
+        <v>0.04112233614560443</v>
       </c>
       <c r="C463">
-        <v>0.14686548623430154</v>
+        <v>0.11749238898744123</v>
       </c>
       <c r="D463">
-        <v>0.22029822935145232</v>
+        <v>0.17623858348116184</v>
       </c>
     </row>
     <row r="464">
@@ -6505,13 +6505,13 @@
         <v>4.62</v>
       </c>
       <c r="B464">
-        <v>0.051180637544273905</v>
+        <v>0.04094451003541912</v>
       </c>
       <c r="C464">
-        <v>0.14623039298363974</v>
+        <v>0.11698431438691179</v>
       </c>
       <c r="D464">
-        <v>0.21934558947545962</v>
+        <v>0.17547647158036767</v>
       </c>
     </row>
     <row r="465">
@@ -6519,13 +6519,13 @@
         <v>4.63</v>
       </c>
       <c r="B465">
-        <v>0.050959793626877026</v>
+        <v>0.04076783490150162</v>
       </c>
       <c r="C465">
-        <v>0.1455994103625058</v>
+        <v>0.11647952829000463</v>
       </c>
       <c r="D465">
-        <v>0.21839911554375868</v>
+        <v>0.17471929243500695</v>
       </c>
     </row>
     <row r="466">
@@ -6533,13 +6533,13 @@
         <v>4.64</v>
       </c>
       <c r="B466">
-        <v>0.05074037604042806</v>
+        <v>0.04059230083234245</v>
       </c>
       <c r="C466">
-        <v>0.1449725029726516</v>
+        <v>0.1159780023781213</v>
       </c>
       <c r="D466">
-        <v>0.2174587544589774</v>
+        <v>0.17396700356718195</v>
       </c>
     </row>
     <row r="467">
@@ -6547,13 +6547,13 @@
         <v>4.65</v>
       </c>
       <c r="B467">
-        <v>0.050522372528616015</v>
+        <v>0.04041789802289281</v>
       </c>
       <c r="C467">
-        <v>0.14434963579604576</v>
+        <v>0.11547970863683663</v>
       </c>
       <c r="D467">
-        <v>0.21652445369406864</v>
+        <v>0.17321956295525492</v>
       </c>
     </row>
     <row r="468">
@@ -6561,13 +6561,13 @@
         <v>4.66</v>
       </c>
       <c r="B468">
-        <v>0.05030577096649413</v>
+        <v>0.0402446167731953</v>
       </c>
       <c r="C468">
-        <v>0.14373077418998323</v>
+        <v>0.11498461935198659</v>
       </c>
       <c r="D468">
-        <v>0.21559616128497483</v>
+        <v>0.1724769290279799</v>
       </c>
     </row>
     <row r="469">
@@ -6575,13 +6575,13 @@
         <v>4.67</v>
       </c>
       <c r="B469">
-        <v>0.05009055935879389</v>
+        <v>0.04007244748703512</v>
       </c>
       <c r="C469">
-        <v>0.14311588388226826</v>
+        <v>0.11449270710581462</v>
       </c>
       <c r="D469">
-        <v>0.2146738258234024</v>
+        <v>0.17173906065872194</v>
       </c>
     </row>
     <row r="470">
@@ -6589,13 +6589,13 @@
         <v>4.68</v>
       </c>
       <c r="B470">
-        <v>0.04987672583826431</v>
+        <v>0.03990138067061144</v>
       </c>
       <c r="C470">
-        <v>0.14250493096646946</v>
+        <v>0.11400394477317556</v>
       </c>
       <c r="D470">
-        <v>0.2137573964497042</v>
+        <v>0.17100591715976335</v>
       </c>
     </row>
     <row r="471">
@@ -6603,13 +6603,13 @@
         <v>4.69</v>
       </c>
       <c r="B471">
-        <v>0.04966425866403589</v>
+        <v>0.039731406931228716</v>
       </c>
       <c r="C471">
-        <v>0.14189788189724542</v>
+        <v>0.11351830551779633</v>
       </c>
       <c r="D471">
-        <v>0.21284682284586814</v>
+        <v>0.1702774582766945</v>
       </c>
     </row>
     <row r="472">
@@ -6617,13 +6617,13 @@
         <v>4.7</v>
       </c>
       <c r="B472">
-        <v>0.04945314622000904</v>
+        <v>0.03956251697600723</v>
       </c>
       <c r="C472">
-        <v>0.14129470348574014</v>
+        <v>0.1130357627885921</v>
       </c>
       <c r="D472">
-        <v>0.2119420552286102</v>
+        <v>0.16955364418288815</v>
       </c>
     </row>
     <row r="473">
@@ -6631,13 +6631,13 @@
         <v>4.71</v>
       </c>
       <c r="B473">
-        <v>0.049243377013266254</v>
+        <v>0.039394701610613</v>
       </c>
       <c r="C473">
-        <v>0.14069536289504644</v>
+        <v>0.11255629031603716</v>
       </c>
       <c r="D473">
-        <v>0.21104304434256965</v>
+        <v>0.16883443547405574</v>
       </c>
     </row>
     <row r="474">
@@ -6645,13 +6645,13 @@
         <v>4.72</v>
       </c>
       <c r="B474">
-        <v>0.049034939672507896</v>
+        <v>0.03922795173800632</v>
       </c>
       <c r="C474">
-        <v>0.14009982763573686</v>
+        <v>0.1120798621085895</v>
       </c>
       <c r="D474">
-        <v>0.2101497414536053</v>
+        <v>0.16811979316288425</v>
       </c>
     </row>
     <row r="475">
@@ -6659,13 +6659,13 @@
         <v>4.73</v>
       </c>
       <c r="B475">
-        <v>0.04882782294651116</v>
+        <v>0.03906225835720893</v>
       </c>
       <c r="C475">
-        <v>0.13950806556146048</v>
+        <v>0.11160645244916839</v>
       </c>
       <c r="D475">
-        <v>0.20926209834219073</v>
+        <v>0.1674096786737526</v>
       </c>
     </row>
     <row r="476">
@@ -6673,13 +6673,13 @@
         <v>4.74</v>
       </c>
       <c r="B476">
-        <v>0.04862201570261175</v>
+        <v>0.03889761256208941</v>
       </c>
       <c r="C476">
-        <v>0.13892004486460502</v>
+        <v>0.11113603589168403</v>
       </c>
       <c r="D476">
-        <v>0.20838006729690753</v>
+        <v>0.16670405383752604</v>
       </c>
     </row>
     <row r="477">
@@ -6687,13 +6687,13 @@
         <v>4.75</v>
       </c>
       <c r="B477">
-        <v>0.04841750692520775</v>
+        <v>0.038734005540166205</v>
       </c>
       <c r="C477">
-        <v>0.13833573407202215</v>
+        <v>0.11066858725761773</v>
       </c>
       <c r="D477">
-        <v>0.20750360110803323</v>
+        <v>0.1660028808864266</v>
       </c>
     </row>
     <row r="478">
@@ -6701,13 +6701,13 @@
         <v>4.76</v>
       </c>
       <c r="B478">
-        <v>0.048214285714285716</v>
+        <v>0.03857142857142857</v>
       </c>
       <c r="C478">
-        <v>0.13775510204081634</v>
+        <v>0.11020408163265306</v>
       </c>
       <c r="D478">
-        <v>0.20663265306122452</v>
+        <v>0.1653061224489796</v>
       </c>
     </row>
     <row r="479">
@@ -6715,13 +6715,13 @@
         <v>4.77</v>
       </c>
       <c r="B479">
-        <v>0.0480123412839682</v>
+        <v>0.03840987302717456</v>
       </c>
       <c r="C479">
-        <v>0.13717811795419488</v>
+        <v>0.1097424943633559</v>
       </c>
       <c r="D479">
-        <v>0.20576717693129232</v>
+        <v>0.16461374154503383</v>
       </c>
     </row>
     <row r="480">
@@ -6729,13 +6729,13 @@
         <v>4.78</v>
       </c>
       <c r="B480">
-        <v>0.047811662961082614</v>
+        <v>0.03824933036886609</v>
       </c>
       <c r="C480">
-        <v>0.1366047513173789</v>
+        <v>0.10928380105390312</v>
       </c>
       <c r="D480">
-        <v>0.20490712697606833</v>
+        <v>0.16392570158085468</v>
       </c>
     </row>
     <row r="481">
@@ -6743,13 +6743,13 @@
         <v>4.79</v>
       </c>
       <c r="B481">
-        <v>0.047612240183750945</v>
+        <v>0.038089792147000756</v>
       </c>
       <c r="C481">
-        <v>0.13603497195357414</v>
+        <v>0.10882797756285931</v>
       </c>
       <c r="D481">
-        <v>0.2040524579303612</v>
+        <v>0.16324196634428895</v>
       </c>
     </row>
     <row r="482">
@@ -6757,13 +6757,13 @@
         <v>4.8</v>
       </c>
       <c r="B482">
-        <v>0.0474140625</v>
+        <v>0.03793125</v>
       </c>
       <c r="C482">
-        <v>0.13546875</v>
+        <v>0.10837500000000001</v>
       </c>
       <c r="D482">
-        <v>0.20320312499999998</v>
+        <v>0.16256250000000003</v>
       </c>
     </row>
     <row r="483">
@@ -6771,13 +6771,13 @@
         <v>4.81</v>
       </c>
       <c r="B483">
-        <v>0.04721711956639192</v>
+        <v>0.03777369565311354</v>
       </c>
       <c r="C483">
-        <v>0.13490605590397692</v>
+        <v>0.10792484472318155</v>
       </c>
       <c r="D483">
-        <v>0.20235908385596538</v>
+        <v>0.16188726708477233</v>
       </c>
     </row>
     <row r="484">
@@ -6785,13 +6785,13 @@
         <v>4.82</v>
       </c>
       <c r="B484">
-        <v>0.04702140114667446</v>
+        <v>0.037617120917339576</v>
       </c>
       <c r="C484">
-        <v>0.1343468604190699</v>
+        <v>0.10747748833525593</v>
       </c>
       <c r="D484">
-        <v>0.20152029062860485</v>
+        <v>0.1612162325028839</v>
       </c>
     </row>
     <row r="485">
@@ -6799,13 +6799,13 @@
         <v>4.83</v>
       </c>
       <c r="B485">
-        <v>0.04682689711045098</v>
+        <v>0.037461517688360785</v>
       </c>
       <c r="C485">
-        <v>0.13379113460128852</v>
+        <v>0.10703290768103083</v>
       </c>
       <c r="D485">
-        <v>0.20068670190193277</v>
+        <v>0.16054936152154625</v>
       </c>
     </row>
     <row r="486">
@@ -6813,13 +6813,13 @@
         <v>4.84</v>
       </c>
       <c r="B486">
-        <v>0.04663359743186941</v>
+        <v>0.037306877945495524</v>
       </c>
       <c r="C486">
-        <v>0.13323884980534118</v>
+        <v>0.10659107984427293</v>
       </c>
       <c r="D486">
-        <v>0.19985827470801176</v>
+        <v>0.1598866197664094</v>
       </c>
     </row>
     <row r="487">
@@ -6827,13 +6827,13 @@
         <v>4.85</v>
       </c>
       <c r="B487">
-        <v>0.046441492188330324</v>
+        <v>0.03715319375066426</v>
       </c>
       <c r="C487">
-        <v>0.1326899776809438</v>
+        <v>0.10615198214475503</v>
       </c>
       <c r="D487">
-        <v>0.19903496652141567</v>
+        <v>0.15922797321713256</v>
       </c>
     </row>
     <row r="488">
@@ -6841,13 +6841,13 @@
         <v>4.86</v>
       </c>
       <c r="B488">
-        <v>0.04625057155921353</v>
+        <v>0.037000457247370826</v>
       </c>
       <c r="C488">
-        <v>0.1321444901691815</v>
+        <v>0.10571559213534522</v>
       </c>
       <c r="D488">
-        <v>0.19821673525377226</v>
+        <v>0.15857338820301783</v>
       </c>
     </row>
     <row r="489">
@@ -6855,13 +6855,13 @@
         <v>4.87</v>
       </c>
       <c r="B489">
-        <v>0.04606082582462294</v>
+        <v>0.03684866065969836</v>
       </c>
       <c r="C489">
-        <v>0.13160235949892268</v>
+        <v>0.10528188759913816</v>
       </c>
       <c r="D489">
-        <v>0.19740353924838402</v>
+        <v>0.15792283139870725</v>
       </c>
     </row>
     <row r="490">
@@ -6869,13 +6869,13 @@
         <v>4.88</v>
       </c>
       <c r="B490">
-        <v>0.045872245364149425</v>
+        <v>0.036697796291319536</v>
       </c>
       <c r="C490">
-        <v>0.13106355818328408</v>
+        <v>0.10485084654662725</v>
       </c>
       <c r="D490">
-        <v>0.19659533727492612</v>
+        <v>0.1572762698199409</v>
       </c>
     </row>
     <row r="491">
@@ -6883,13 +6883,13 @@
         <v>4.89</v>
       </c>
       <c r="B491">
-        <v>0.04568482065565133</v>
+        <v>0.03654785652452107</v>
       </c>
       <c r="C491">
-        <v>0.13052805901614667</v>
+        <v>0.10442244721291734</v>
       </c>
       <c r="D491">
-        <v>0.19579208852422</v>
+        <v>0.15663367081937601</v>
       </c>
     </row>
     <row r="492">
@@ -6897,13 +6897,13 @@
         <v>4.9</v>
       </c>
       <c r="B492">
-        <v>0.045498542274052464</v>
+        <v>0.03639883381924198</v>
       </c>
       <c r="C492">
-        <v>0.12999583506872134</v>
+        <v>0.10399666805497708</v>
       </c>
       <c r="D492">
-        <v>0.194993752603082</v>
+        <v>0.1559950020824656</v>
       </c>
     </row>
     <row r="493">
@@ -6911,13 +6911,13 @@
         <v>4.91</v>
       </c>
       <c r="B493">
-        <v>0.04531340089015724</v>
+        <v>0.036250720712125796</v>
       </c>
       <c r="C493">
-        <v>0.12946685968616356</v>
+        <v>0.10357348774893085</v>
       </c>
       <c r="D493">
-        <v>0.19420028952924534</v>
+        <v>0.1553602316233963</v>
       </c>
     </row>
     <row r="494">
@@ -6925,13 +6925,13 @@
         <v>4.92</v>
       </c>
       <c r="B494">
-        <v>0.04512938726948244</v>
+        <v>0.03610350981558596</v>
       </c>
       <c r="C494">
-        <v>0.12894110648423557</v>
+        <v>0.10315288518738847</v>
       </c>
       <c r="D494">
-        <v>0.19341165972635335</v>
+        <v>0.1547293277810827</v>
       </c>
     </row>
     <row r="495">
@@ -6939,13 +6939,13 @@
         <v>4.93</v>
       </c>
       <c r="B495">
-        <v>0.04494649227110582</v>
+        <v>0.03595719381688466</v>
       </c>
       <c r="C495">
-        <v>0.12841854934601665</v>
+        <v>0.10273483947681333</v>
       </c>
       <c r="D495">
-        <v>0.19262782401902498</v>
+        <v>0.15410225921522</v>
       </c>
     </row>
     <row r="496">
@@ -6953,13 +6953,13 @@
         <v>4.94</v>
       </c>
       <c r="B496">
-        <v>0.044764706846530826</v>
+        <v>0.035811765477224665</v>
       </c>
       <c r="C496">
-        <v>0.1278991624186595</v>
+        <v>0.10231932993492762</v>
       </c>
       <c r="D496">
-        <v>0.19184874362798926</v>
+        <v>0.15347899490239142</v>
       </c>
     </row>
     <row r="497">
@@ -6967,13 +6967,13 @@
         <v>4.95</v>
       </c>
       <c r="B497">
-        <v>0.04458402203856749</v>
+        <v>0.03566721763085399</v>
       </c>
       <c r="C497">
-        <v>0.12738292011019284</v>
+        <v>0.10190633608815426</v>
       </c>
       <c r="D497">
-        <v>0.19107438016528927</v>
+        <v>0.1528595041322314</v>
       </c>
     </row>
     <row r="498">
@@ -6981,13 +6981,13 @@
         <v>4.96</v>
       </c>
       <c r="B498">
-        <v>0.04440442898022892</v>
+        <v>0.03552354318418314</v>
       </c>
       <c r="C498">
-        <v>0.12686979708636836</v>
+        <v>0.10149583766909469</v>
       </c>
       <c r="D498">
-        <v>0.19030469562955254</v>
+        <v>0.15224375650364202</v>
       </c>
     </row>
     <row r="499">
@@ -6995,13 +6995,13 @@
         <v>4.97</v>
       </c>
       <c r="B499">
-        <v>0.04422591889364355</v>
+        <v>0.035380735114914845</v>
       </c>
       <c r="C499">
-        <v>0.12635976826755302</v>
+        <v>0.10108781461404241</v>
       </c>
       <c r="D499">
-        <v>0.18953965240132953</v>
+        <v>0.1516317219210636</v>
       </c>
     </row>
     <row r="500">
@@ -7009,13 +7009,13 @@
         <v>4.98</v>
       </c>
       <c r="B500">
-        <v>0.044048483088982425</v>
+        <v>0.035238786471185946</v>
       </c>
       <c r="C500">
-        <v>0.12585280882566408</v>
+        <v>0.10068224706053128</v>
       </c>
       <c r="D500">
-        <v>0.1887792132384961</v>
+        <v>0.1510233705907969</v>
       </c>
     </row>
     <row r="501">
@@ -7023,13 +7023,13 @@
         <v>4.99</v>
       </c>
       <c r="B501">
-        <v>0.04387211296340175</v>
+        <v>0.0350976903707214</v>
       </c>
       <c r="C501">
-        <v>0.12534889418114786</v>
+        <v>0.10027911534491829</v>
       </c>
       <c r="D501">
-        <v>0.1880233412717218</v>
+        <v>0.15041867301737744</v>
       </c>
     </row>
     <row r="502">
@@ -7037,13 +7037,13 @@
         <v>5.0</v>
       </c>
       <c r="B502">
-        <v>0.0436968</v>
+        <v>0.03495744</v>
       </c>
       <c r="C502">
-        <v>0.124848</v>
+        <v>0.0998784</v>
       </c>
       <c r="D502">
-        <v>0.187272</v>
+        <v>0.1498176</v>
       </c>
     </row>
   </sheetData>
